--- a/model performance comparison/Ratio_Cfree_Cnominal/ThisStudy_data/Fischer model.xlsx
+++ b/model performance comparison/Ratio_Cfree_Cnominal/ThisStudy_data/Fischer model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Validation_Lucie\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\TAMU PHD\MassBalance project\Paper writing\R1\model comparison_update_based reviewer\Validation_Lucie\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C068E6F9-6D7B-4CB3-991B-358889EF59AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{816AE452-E15E-4F35-9229-649697CC089D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="13875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Model structure" sheetId="1" r:id="rId1"/>
@@ -428,7 +428,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="109">
   <si>
     <t>Assumptions:</t>
   </si>
@@ -1134,6 +1134,12 @@
   <si>
     <t>335-76-2</t>
   </si>
+  <si>
+    <t>˂1</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
 </sst>
 </file>
 
@@ -1145,7 +1151,7 @@
     <numFmt numFmtId="178" formatCode="0.00000000000"/>
     <numFmt numFmtId="179" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1287,6 +1293,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
       <name val="Helvetica"/>
       <family val="2"/>
     </font>
@@ -1665,7 +1677,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1902,6 +1914,10 @@
       <alignment horizontal="center" vertical="center"/>
       <protection hidden="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1937,6 +1953,143 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2025,12 +2178,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2058,138 +2205,7 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="12" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -3420,33 +3436,33 @@
     </row>
     <row r="2" spans="1:32" ht="17.649999999999999" x14ac:dyDescent="0.5">
       <c r="A2" s="7"/>
-      <c r="B2" s="96" t="s">
+      <c r="B2" s="97" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="97"/>
-      <c r="D2" s="97"/>
-      <c r="E2" s="97"/>
-      <c r="F2" s="97"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="98"/>
+      <c r="G2" s="98"/>
+      <c r="H2" s="99"/>
       <c r="I2" s="7"/>
-      <c r="J2" s="87" t="s">
+      <c r="J2" s="88" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="88"/>
-      <c r="L2" s="88"/>
-      <c r="M2" s="88"/>
-      <c r="N2" s="88"/>
-      <c r="O2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
+      <c r="M2" s="89"/>
+      <c r="N2" s="89"/>
+      <c r="O2" s="90"/>
       <c r="P2" s="7"/>
-      <c r="Q2" s="87" t="s">
+      <c r="Q2" s="88" t="s">
         <v>60</v>
       </c>
-      <c r="R2" s="88"/>
-      <c r="S2" s="88"/>
-      <c r="T2" s="88"/>
-      <c r="U2" s="88"/>
-      <c r="V2" s="89"/>
+      <c r="R2" s="89"/>
+      <c r="S2" s="89"/>
+      <c r="T2" s="89"/>
+      <c r="U2" s="89"/>
+      <c r="V2" s="90"/>
       <c r="W2" s="7"/>
       <c r="X2" s="7"/>
       <c r="Y2" s="7"/>
@@ -3472,19 +3488,19 @@
       <c r="G3" s="26"/>
       <c r="H3" s="27"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="90"/>
-      <c r="K3" s="91"/>
-      <c r="L3" s="91"/>
-      <c r="M3" s="91"/>
-      <c r="N3" s="91"/>
-      <c r="O3" s="92"/>
+      <c r="J3" s="91"/>
+      <c r="K3" s="92"/>
+      <c r="L3" s="92"/>
+      <c r="M3" s="92"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="93"/>
       <c r="P3" s="7"/>
-      <c r="Q3" s="90"/>
-      <c r="R3" s="91"/>
-      <c r="S3" s="91"/>
-      <c r="T3" s="91"/>
-      <c r="U3" s="91"/>
-      <c r="V3" s="92"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="92"/>
+      <c r="S3" s="92"/>
+      <c r="T3" s="92"/>
+      <c r="U3" s="92"/>
+      <c r="V3" s="93"/>
       <c r="W3" s="7"/>
       <c r="X3" s="7"/>
       <c r="Y3" s="7"/>
@@ -3508,19 +3524,19 @@
       <c r="G4" s="29"/>
       <c r="H4" s="31"/>
       <c r="I4" s="7"/>
-      <c r="J4" s="93"/>
-      <c r="K4" s="94"/>
-      <c r="L4" s="94"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="95"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="95"/>
+      <c r="L4" s="95"/>
+      <c r="M4" s="95"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="96"/>
       <c r="P4" s="7"/>
-      <c r="Q4" s="93"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="94"/>
-      <c r="V4" s="95"/>
+      <c r="Q4" s="94"/>
+      <c r="R4" s="95"/>
+      <c r="S4" s="95"/>
+      <c r="T4" s="95"/>
+      <c r="U4" s="95"/>
+      <c r="V4" s="96"/>
       <c r="W4" s="7"/>
       <c r="X4" s="7"/>
       <c r="Y4" s="7"/>
@@ -13996,8 +14012,8 @@
       <c r="D1" s="7"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
-      <c r="G1" s="154"/>
-      <c r="H1" s="154"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
       <c r="I1" s="7"/>
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
@@ -14030,19 +14046,19 @@
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
       <c r="F2" s="7"/>
-      <c r="G2" s="154"/>
-      <c r="H2" s="154"/>
-      <c r="I2" s="99" t="s">
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="138" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="100"/>
-      <c r="K2" s="100"/>
-      <c r="L2" s="100"/>
-      <c r="M2" s="100"/>
-      <c r="N2" s="100"/>
-      <c r="O2" s="100"/>
-      <c r="P2" s="100"/>
-      <c r="Q2" s="101"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
+      <c r="N2" s="139"/>
+      <c r="O2" s="139"/>
+      <c r="P2" s="139"/>
+      <c r="Q2" s="140"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
@@ -14066,17 +14082,17 @@
       <c r="D3" s="7"/>
       <c r="E3" s="7"/>
       <c r="F3" s="7"/>
-      <c r="G3" s="154"/>
-      <c r="H3" s="154"/>
-      <c r="I3" s="102"/>
-      <c r="J3" s="103"/>
-      <c r="K3" s="103"/>
-      <c r="L3" s="103"/>
-      <c r="M3" s="103"/>
-      <c r="N3" s="103"/>
-      <c r="O3" s="103"/>
-      <c r="P3" s="103"/>
-      <c r="Q3" s="104"/>
+      <c r="G3" s="125"/>
+      <c r="H3" s="125"/>
+      <c r="I3" s="141"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="142"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="142"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="143"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
@@ -14100,17 +14116,17 @@
       <c r="D4" s="7"/>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
-      <c r="G4" s="154"/>
-      <c r="H4" s="154"/>
-      <c r="I4" s="105"/>
-      <c r="J4" s="106"/>
-      <c r="K4" s="106"/>
-      <c r="L4" s="106"/>
-      <c r="M4" s="106"/>
-      <c r="N4" s="106"/>
-      <c r="O4" s="106"/>
-      <c r="P4" s="106"/>
-      <c r="Q4" s="107"/>
+      <c r="G4" s="125"/>
+      <c r="H4" s="125"/>
+      <c r="I4" s="144"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
+      <c r="O4" s="145"/>
+      <c r="P4" s="145"/>
+      <c r="Q4" s="146"/>
       <c r="R4" s="7"/>
       <c r="S4" s="7"/>
       <c r="T4" s="7"/>
@@ -14134,19 +14150,19 @@
       <c r="D5" s="7"/>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
-      <c r="G5" s="154"/>
-      <c r="H5" s="154"/>
-      <c r="I5" s="108" t="s">
+      <c r="G5" s="125"/>
+      <c r="H5" s="125"/>
+      <c r="I5" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="J5" s="109"/>
-      <c r="K5" s="109"/>
-      <c r="L5" s="109"/>
-      <c r="M5" s="109"/>
-      <c r="N5" s="109"/>
-      <c r="O5" s="109"/>
-      <c r="P5" s="109"/>
-      <c r="Q5" s="110"/>
+      <c r="J5" s="148"/>
+      <c r="K5" s="148"/>
+      <c r="L5" s="148"/>
+      <c r="M5" s="148"/>
+      <c r="N5" s="148"/>
+      <c r="O5" s="148"/>
+      <c r="P5" s="148"/>
+      <c r="Q5" s="149"/>
       <c r="R5" s="7"/>
       <c r="S5" s="7"/>
       <c r="T5" s="7"/>
@@ -14170,8 +14186,8 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="154"/>
-      <c r="H6" s="154"/>
+      <c r="G6" s="125"/>
+      <c r="H6" s="125"/>
       <c r="I6" s="50" t="s">
         <v>51</v>
       </c>
@@ -14181,14 +14197,14 @@
       <c r="K6" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L6" s="151" t="s">
+      <c r="L6" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="152"/>
-      <c r="N6" s="152"/>
-      <c r="O6" s="152"/>
-      <c r="P6" s="152"/>
-      <c r="Q6" s="153"/>
+      <c r="M6" s="118"/>
+      <c r="N6" s="118"/>
+      <c r="O6" s="118"/>
+      <c r="P6" s="118"/>
+      <c r="Q6" s="119"/>
       <c r="R6" s="7"/>
       <c r="S6" s="7"/>
       <c r="T6" s="7"/>
@@ -14212,8 +14228,8 @@
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
-      <c r="G7" s="154"/>
-      <c r="H7" s="154"/>
+      <c r="G7" s="125"/>
+      <c r="H7" s="125"/>
       <c r="I7" s="51" t="s">
         <v>21</v>
       </c>
@@ -14225,14 +14241,14 @@
         <f>J7/J7</f>
         <v>1</v>
       </c>
-      <c r="L7" s="145" t="s">
+      <c r="L7" s="100" t="s">
         <v>70</v>
       </c>
-      <c r="M7" s="146"/>
-      <c r="N7" s="146"/>
-      <c r="O7" s="146"/>
-      <c r="P7" s="146"/>
-      <c r="Q7" s="147"/>
+      <c r="M7" s="101"/>
+      <c r="N7" s="101"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="101"/>
+      <c r="Q7" s="102"/>
       <c r="R7" s="7"/>
       <c r="S7" s="7"/>
       <c r="T7" s="7"/>
@@ -14251,15 +14267,15 @@
     </row>
     <row r="8" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="7"/>
-      <c r="B8" s="126" t="s">
+      <c r="B8" s="163" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="127"/>
-      <c r="D8" s="127"/>
-      <c r="E8" s="127"/>
-      <c r="F8" s="128"/>
-      <c r="G8" s="154"/>
-      <c r="H8" s="154"/>
+      <c r="C8" s="164"/>
+      <c r="D8" s="164"/>
+      <c r="E8" s="164"/>
+      <c r="F8" s="165"/>
+      <c r="G8" s="125"/>
+      <c r="H8" s="125"/>
       <c r="I8" s="52" t="s">
         <v>6</v>
       </c>
@@ -14271,14 +14287,14 @@
         <f>J8/J7</f>
         <v>0.99456699999999998</v>
       </c>
-      <c r="L8" s="145" t="s">
+      <c r="L8" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M8" s="146"/>
-      <c r="N8" s="146"/>
-      <c r="O8" s="146"/>
-      <c r="P8" s="146"/>
-      <c r="Q8" s="147"/>
+      <c r="M8" s="101"/>
+      <c r="N8" s="101"/>
+      <c r="O8" s="101"/>
+      <c r="P8" s="101"/>
+      <c r="Q8" s="102"/>
       <c r="R8" s="7"/>
       <c r="S8" s="7"/>
       <c r="T8" s="7"/>
@@ -14297,13 +14313,13 @@
     </row>
     <row r="9" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="7"/>
-      <c r="B9" s="129"/>
-      <c r="C9" s="130"/>
-      <c r="D9" s="130"/>
-      <c r="E9" s="130"/>
-      <c r="F9" s="131"/>
-      <c r="G9" s="154"/>
-      <c r="H9" s="154"/>
+      <c r="B9" s="166"/>
+      <c r="C9" s="167"/>
+      <c r="D9" s="167"/>
+      <c r="E9" s="167"/>
+      <c r="F9" s="168"/>
+      <c r="G9" s="125"/>
+      <c r="H9" s="125"/>
       <c r="I9" s="51" t="s">
         <v>8</v>
       </c>
@@ -14315,14 +14331,14 @@
         <f>J9/J7</f>
         <v>5.2759999999999994E-3</v>
       </c>
-      <c r="L9" s="145" t="s">
+      <c r="L9" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M9" s="146"/>
-      <c r="N9" s="146"/>
-      <c r="O9" s="146"/>
-      <c r="P9" s="146"/>
-      <c r="Q9" s="147"/>
+      <c r="M9" s="101"/>
+      <c r="N9" s="101"/>
+      <c r="O9" s="101"/>
+      <c r="P9" s="101"/>
+      <c r="Q9" s="102"/>
       <c r="R9" s="7"/>
       <c r="S9" s="7"/>
       <c r="T9" s="7"/>
@@ -14341,13 +14357,13 @@
     </row>
     <row r="10" spans="1:32" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="7"/>
-      <c r="B10" s="132"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="133"/>
-      <c r="E10" s="133"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="154"/>
-      <c r="H10" s="154"/>
+      <c r="B10" s="169"/>
+      <c r="C10" s="170"/>
+      <c r="D10" s="170"/>
+      <c r="E10" s="170"/>
+      <c r="F10" s="171"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
       <c r="I10" s="52" t="s">
         <v>9</v>
       </c>
@@ -14359,14 +14375,14 @@
         <f>J10/J7</f>
         <v>1.5700000000000002E-4</v>
       </c>
-      <c r="L10" s="145" t="s">
+      <c r="L10" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M10" s="146"/>
-      <c r="N10" s="146"/>
-      <c r="O10" s="146"/>
-      <c r="P10" s="146"/>
-      <c r="Q10" s="147"/>
+      <c r="M10" s="101"/>
+      <c r="N10" s="101"/>
+      <c r="O10" s="101"/>
+      <c r="P10" s="101"/>
+      <c r="Q10" s="102"/>
       <c r="R10" s="7"/>
       <c r="S10" s="7"/>
       <c r="T10" s="7"/>
@@ -14385,24 +14401,24 @@
     </row>
     <row r="11" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
-      <c r="B11" s="135" t="s">
+      <c r="B11" s="128" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="136"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="136"/>
-      <c r="F11" s="137"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="154"/>
-      <c r="I11" s="170"/>
-      <c r="J11" s="170"/>
-      <c r="K11" s="170"/>
-      <c r="L11" s="170"/>
-      <c r="M11" s="170"/>
-      <c r="N11" s="170"/>
-      <c r="O11" s="170"/>
-      <c r="P11" s="170"/>
-      <c r="Q11" s="170"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="129"/>
+      <c r="F11" s="130"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="116"/>
+      <c r="J11" s="116"/>
+      <c r="K11" s="116"/>
+      <c r="L11" s="116"/>
+      <c r="M11" s="116"/>
+      <c r="N11" s="116"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="116"/>
+      <c r="Q11" s="116"/>
       <c r="R11" s="7"/>
       <c r="S11" s="7"/>
       <c r="T11" s="7"/>
@@ -14421,13 +14437,13 @@
     </row>
     <row r="12" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="7"/>
-      <c r="B12" s="138"/>
-      <c r="C12" s="139"/>
-      <c r="D12" s="139"/>
-      <c r="E12" s="139"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="154"/>
-      <c r="H12" s="154"/>
+      <c r="B12" s="131"/>
+      <c r="C12" s="132"/>
+      <c r="D12" s="132"/>
+      <c r="E12" s="132"/>
+      <c r="F12" s="133"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
       <c r="I12" s="50" t="s">
         <v>53</v>
       </c>
@@ -14437,14 +14453,14 @@
       <c r="K12" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L12" s="151" t="s">
+      <c r="L12" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="152"/>
-      <c r="N12" s="152"/>
-      <c r="O12" s="152"/>
-      <c r="P12" s="152"/>
-      <c r="Q12" s="153"/>
+      <c r="M12" s="118"/>
+      <c r="N12" s="118"/>
+      <c r="O12" s="118"/>
+      <c r="P12" s="118"/>
+      <c r="Q12" s="119"/>
       <c r="R12" s="7"/>
       <c r="S12" s="7"/>
       <c r="T12" s="7"/>
@@ -14463,17 +14479,17 @@
     </row>
     <row r="13" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="8"/>
-      <c r="B13" s="124" t="s">
+      <c r="B13" s="120" t="s">
         <v>4</v>
       </c>
-      <c r="C13" s="125"/>
-      <c r="D13" s="114" t="s">
+      <c r="C13" s="121"/>
+      <c r="D13" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="114"/>
-      <c r="F13" s="114"/>
-      <c r="G13" s="154"/>
-      <c r="H13" s="154"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
       <c r="I13" s="51" t="s">
         <v>5</v>
       </c>
@@ -14485,14 +14501,14 @@
         <f>J13/J13</f>
         <v>1</v>
       </c>
-      <c r="L13" s="145" t="s">
+      <c r="L13" s="100" t="s">
         <v>73</v>
       </c>
-      <c r="M13" s="146"/>
-      <c r="N13" s="146"/>
-      <c r="O13" s="146"/>
-      <c r="P13" s="146"/>
-      <c r="Q13" s="147"/>
+      <c r="M13" s="101"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="101"/>
+      <c r="Q13" s="102"/>
       <c r="R13" s="7"/>
       <c r="S13" s="7"/>
       <c r="T13" s="7"/>
@@ -14517,13 +14533,13 @@
       <c r="C14" s="44">
         <v>50</v>
       </c>
-      <c r="D14" s="115" t="s">
+      <c r="D14" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="115"/>
-      <c r="F14" s="115"/>
-      <c r="G14" s="154"/>
-      <c r="H14" s="154"/>
+      <c r="E14" s="154"/>
+      <c r="F14" s="154"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
       <c r="I14" s="52" t="s">
         <v>45</v>
       </c>
@@ -14535,14 +14551,14 @@
         <f>J14/J13</f>
         <v>0.99456699999999998</v>
       </c>
-      <c r="L14" s="148" t="s">
+      <c r="L14" s="122" t="s">
         <v>72</v>
       </c>
-      <c r="M14" s="149"/>
-      <c r="N14" s="149"/>
-      <c r="O14" s="149"/>
-      <c r="P14" s="149"/>
-      <c r="Q14" s="150"/>
+      <c r="M14" s="123"/>
+      <c r="N14" s="123"/>
+      <c r="O14" s="123"/>
+      <c r="P14" s="123"/>
+      <c r="Q14" s="124"/>
       <c r="R14" s="7"/>
       <c r="S14" s="7"/>
       <c r="T14" s="7"/>
@@ -14567,13 +14583,13 @@
       <c r="C15" s="32" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="116" t="s">
+      <c r="D15" s="155" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="116"/>
-      <c r="F15" s="116"/>
-      <c r="G15" s="154"/>
-      <c r="H15" s="154"/>
+      <c r="E15" s="155"/>
+      <c r="F15" s="155"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
       <c r="I15" s="51" t="s">
         <v>46</v>
       </c>
@@ -14585,14 +14601,14 @@
         <f>J15/J13</f>
         <v>5.2759999999999994E-3</v>
       </c>
-      <c r="L15" s="145" t="s">
+      <c r="L15" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M15" s="146"/>
-      <c r="N15" s="146"/>
-      <c r="O15" s="146"/>
-      <c r="P15" s="146"/>
-      <c r="Q15" s="147"/>
+      <c r="M15" s="101"/>
+      <c r="N15" s="101"/>
+      <c r="O15" s="101"/>
+      <c r="P15" s="101"/>
+      <c r="Q15" s="102"/>
       <c r="R15" s="7"/>
       <c r="S15" s="7"/>
       <c r="T15" s="7"/>
@@ -14617,13 +14633,13 @@
       <c r="C16" s="45">
         <v>0.9</v>
       </c>
-      <c r="D16" s="117" t="s">
+      <c r="D16" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="118"/>
-      <c r="F16" s="119"/>
-      <c r="G16" s="154"/>
-      <c r="H16" s="154"/>
+      <c r="E16" s="157"/>
+      <c r="F16" s="158"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
       <c r="I16" s="52" t="s">
         <v>47</v>
       </c>
@@ -14635,14 +14651,14 @@
         <f>J16/J13</f>
         <v>1.5700000000000002E-4</v>
       </c>
-      <c r="L16" s="145" t="s">
+      <c r="L16" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M16" s="146"/>
-      <c r="N16" s="146"/>
-      <c r="O16" s="146"/>
-      <c r="P16" s="146"/>
-      <c r="Q16" s="147"/>
+      <c r="M16" s="101"/>
+      <c r="N16" s="101"/>
+      <c r="O16" s="101"/>
+      <c r="P16" s="101"/>
+      <c r="Q16" s="102"/>
       <c r="R16" s="7"/>
       <c r="S16" s="7"/>
       <c r="T16" s="7"/>
@@ -14667,22 +14683,22 @@
       <c r="C17" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="D17" s="120" t="s">
+      <c r="D17" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="154"/>
-      <c r="H17" s="154"/>
-      <c r="I17" s="148"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="149"/>
-      <c r="M17" s="149"/>
-      <c r="N17" s="149"/>
-      <c r="O17" s="149"/>
-      <c r="P17" s="149"/>
-      <c r="Q17" s="150"/>
+      <c r="E17" s="160"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="122"/>
+      <c r="J17" s="123"/>
+      <c r="K17" s="123"/>
+      <c r="L17" s="123"/>
+      <c r="M17" s="123"/>
+      <c r="N17" s="123"/>
+      <c r="O17" s="123"/>
+      <c r="P17" s="123"/>
+      <c r="Q17" s="124"/>
       <c r="R17" s="7"/>
       <c r="S17" s="7"/>
       <c r="T17" s="7"/>
@@ -14707,13 +14723,13 @@
       <c r="C18" s="45">
         <v>0.1</v>
       </c>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="156" t="s">
         <v>43</v>
       </c>
-      <c r="E18" s="118"/>
-      <c r="F18" s="119"/>
-      <c r="G18" s="154"/>
-      <c r="H18" s="154"/>
+      <c r="E18" s="157"/>
+      <c r="F18" s="158"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
       <c r="I18" s="50" t="s">
         <v>31</v>
       </c>
@@ -14723,14 +14739,14 @@
       <c r="K18" s="50" t="s">
         <v>48</v>
       </c>
-      <c r="L18" s="151" t="s">
+      <c r="L18" s="117" t="s">
         <v>41</v>
       </c>
-      <c r="M18" s="152"/>
-      <c r="N18" s="152"/>
-      <c r="O18" s="152"/>
-      <c r="P18" s="152"/>
-      <c r="Q18" s="153"/>
+      <c r="M18" s="118"/>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="118"/>
+      <c r="Q18" s="119"/>
       <c r="R18" s="7"/>
       <c r="S18" s="7"/>
       <c r="T18" s="7"/>
@@ -14749,13 +14765,13 @@
     </row>
     <row r="19" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="7"/>
-      <c r="B19" s="116"/>
-      <c r="C19" s="116"/>
-      <c r="D19" s="116"/>
-      <c r="E19" s="116"/>
-      <c r="F19" s="116"/>
-      <c r="G19" s="154"/>
-      <c r="H19" s="154"/>
+      <c r="B19" s="155"/>
+      <c r="C19" s="155"/>
+      <c r="D19" s="155"/>
+      <c r="E19" s="155"/>
+      <c r="F19" s="155"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
       <c r="I19" s="51" t="s">
         <v>5</v>
       </c>
@@ -14767,14 +14783,14 @@
         <f>J19/J19</f>
         <v>1</v>
       </c>
-      <c r="L19" s="145" t="s">
+      <c r="L19" s="100" t="s">
         <v>57</v>
       </c>
-      <c r="M19" s="146"/>
-      <c r="N19" s="146"/>
-      <c r="O19" s="146"/>
-      <c r="P19" s="146"/>
-      <c r="Q19" s="147"/>
+      <c r="M19" s="101"/>
+      <c r="N19" s="101"/>
+      <c r="O19" s="101"/>
+      <c r="P19" s="101"/>
+      <c r="Q19" s="102"/>
       <c r="R19" s="7"/>
       <c r="S19" s="7"/>
       <c r="T19" s="7"/>
@@ -14793,17 +14809,17 @@
     </row>
     <row r="20" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="7"/>
-      <c r="B20" s="124" t="s">
+      <c r="B20" s="120" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="125"/>
-      <c r="D20" s="114" t="s">
+      <c r="C20" s="121"/>
+      <c r="D20" s="153" t="s">
         <v>41</v>
       </c>
-      <c r="E20" s="114"/>
-      <c r="F20" s="114"/>
-      <c r="G20" s="154"/>
-      <c r="H20" s="154"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
       <c r="I20" s="52" t="s">
         <v>45</v>
       </c>
@@ -14815,14 +14831,14 @@
         <f>J20/J19</f>
         <v>0.87354229684316542</v>
       </c>
-      <c r="L20" s="145" t="s">
+      <c r="L20" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M20" s="146"/>
-      <c r="N20" s="146"/>
-      <c r="O20" s="146"/>
-      <c r="P20" s="146"/>
-      <c r="Q20" s="147"/>
+      <c r="M20" s="101"/>
+      <c r="N20" s="101"/>
+      <c r="O20" s="101"/>
+      <c r="P20" s="101"/>
+      <c r="Q20" s="102"/>
       <c r="R20" s="7"/>
       <c r="S20" s="7"/>
       <c r="T20" s="7"/>
@@ -14847,13 +14863,13 @@
       <c r="C21" s="44" t="s">
         <v>77</v>
       </c>
-      <c r="D21" s="120" t="s">
+      <c r="D21" s="159" t="s">
         <v>63</v>
       </c>
-      <c r="E21" s="121"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="154"/>
-      <c r="H21" s="154"/>
+      <c r="E21" s="160"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
       <c r="I21" s="51" t="s">
         <v>46</v>
       </c>
@@ -14865,14 +14881,14 @@
         <f>J21/J19</f>
         <v>9.4560212233021856E-2</v>
       </c>
-      <c r="L21" s="145" t="s">
+      <c r="L21" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M21" s="146"/>
-      <c r="N21" s="146"/>
-      <c r="O21" s="146"/>
-      <c r="P21" s="146"/>
-      <c r="Q21" s="147"/>
+      <c r="M21" s="101"/>
+      <c r="N21" s="101"/>
+      <c r="O21" s="101"/>
+      <c r="P21" s="101"/>
+      <c r="Q21" s="102"/>
       <c r="R21" s="7"/>
       <c r="S21" s="7"/>
       <c r="T21" s="7"/>
@@ -14897,13 +14913,13 @@
       <c r="C22" s="46">
         <v>1.0000000000000001E-30</v>
       </c>
-      <c r="D22" s="123" t="s">
+      <c r="D22" s="162" t="s">
         <v>69</v>
       </c>
-      <c r="E22" s="123"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="154"/>
-      <c r="H22" s="154"/>
+      <c r="E22" s="162"/>
+      <c r="F22" s="162"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
       <c r="I22" s="53" t="s">
         <v>47</v>
       </c>
@@ -14915,14 +14931,14 @@
         <f>J22/J19</f>
         <v>3.1897490923812694E-2</v>
       </c>
-      <c r="L22" s="145" t="s">
+      <c r="L22" s="100" t="s">
         <v>71</v>
       </c>
-      <c r="M22" s="146"/>
-      <c r="N22" s="146"/>
-      <c r="O22" s="146"/>
-      <c r="P22" s="146"/>
-      <c r="Q22" s="147"/>
+      <c r="M22" s="101"/>
+      <c r="N22" s="101"/>
+      <c r="O22" s="101"/>
+      <c r="P22" s="101"/>
+      <c r="Q22" s="102"/>
       <c r="R22" s="7"/>
       <c r="S22" s="7"/>
       <c r="T22" s="7"/>
@@ -14941,22 +14957,22 @@
     </row>
     <row r="23" spans="1:32" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A23" s="7"/>
-      <c r="B23" s="111"/>
-      <c r="C23" s="112"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="154"/>
-      <c r="H23" s="154"/>
-      <c r="I23" s="165"/>
-      <c r="J23" s="166"/>
-      <c r="K23" s="166"/>
-      <c r="L23" s="166"/>
-      <c r="M23" s="166"/>
-      <c r="N23" s="166"/>
-      <c r="O23" s="166"/>
-      <c r="P23" s="166"/>
-      <c r="Q23" s="167"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="152"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="111"/>
+      <c r="J23" s="112"/>
+      <c r="K23" s="112"/>
+      <c r="L23" s="112"/>
+      <c r="M23" s="112"/>
+      <c r="N23" s="112"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="112"/>
+      <c r="Q23" s="113"/>
       <c r="R23" s="7"/>
       <c r="S23" s="7"/>
       <c r="T23" s="7"/>
@@ -14975,26 +14991,26 @@
     </row>
     <row r="24" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="7"/>
-      <c r="B24" s="135" t="s">
+      <c r="B24" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="C24" s="136"/>
-      <c r="D24" s="136"/>
-      <c r="E24" s="136"/>
-      <c r="F24" s="137"/>
-      <c r="G24" s="154"/>
-      <c r="H24" s="154"/>
-      <c r="I24" s="159" t="s">
+      <c r="C24" s="129"/>
+      <c r="D24" s="129"/>
+      <c r="E24" s="129"/>
+      <c r="F24" s="130"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="105" t="s">
         <v>44</v>
       </c>
-      <c r="J24" s="160"/>
-      <c r="K24" s="160"/>
-      <c r="L24" s="160"/>
-      <c r="M24" s="160"/>
-      <c r="N24" s="160"/>
-      <c r="O24" s="160"/>
-      <c r="P24" s="160"/>
-      <c r="Q24" s="161"/>
+      <c r="J24" s="106"/>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
+      <c r="M24" s="106"/>
+      <c r="N24" s="106"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="106"/>
+      <c r="Q24" s="107"/>
       <c r="R24" s="7"/>
       <c r="S24" s="7"/>
       <c r="T24" s="7"/>
@@ -15013,22 +15029,22 @@
     </row>
     <row r="25" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="7"/>
-      <c r="B25" s="138"/>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="154"/>
-      <c r="H25" s="154"/>
-      <c r="I25" s="162"/>
-      <c r="J25" s="163"/>
-      <c r="K25" s="163"/>
-      <c r="L25" s="163"/>
-      <c r="M25" s="163"/>
-      <c r="N25" s="163"/>
-      <c r="O25" s="163"/>
-      <c r="P25" s="163"/>
-      <c r="Q25" s="164"/>
+      <c r="B25" s="131"/>
+      <c r="C25" s="132"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="133"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="108"/>
+      <c r="J25" s="109"/>
+      <c r="K25" s="109"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+      <c r="O25" s="109"/>
+      <c r="P25" s="109"/>
+      <c r="Q25" s="110"/>
       <c r="R25" s="7"/>
       <c r="S25" s="7"/>
       <c r="T25" s="7"/>
@@ -15047,48 +15063,48 @@
     </row>
     <row r="26" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="7"/>
-      <c r="B26" s="157" t="s">
+      <c r="B26" s="126" t="s">
         <v>11</v>
       </c>
-      <c r="C26" s="157" t="s">
+      <c r="C26" s="126" t="s">
         <v>12</v>
       </c>
-      <c r="D26" s="141" t="s">
+      <c r="D26" s="134" t="s">
         <v>49</v>
       </c>
-      <c r="E26" s="141" t="s">
+      <c r="E26" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="F26" s="143" t="s">
+      <c r="F26" s="136" t="s">
         <v>68</v>
       </c>
-      <c r="G26" s="154"/>
-      <c r="H26" s="154"/>
-      <c r="I26" s="168" t="s">
+      <c r="G26" s="125"/>
+      <c r="H26" s="125"/>
+      <c r="I26" s="114" t="s">
         <v>55</v>
       </c>
-      <c r="J26" s="168" t="s">
+      <c r="J26" s="114" t="s">
         <v>56</v>
       </c>
-      <c r="K26" s="155" t="s">
+      <c r="K26" s="103" t="s">
         <v>76</v>
       </c>
-      <c r="L26" s="155" t="s">
+      <c r="L26" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="M26" s="155" t="s">
+      <c r="M26" s="103" t="s">
         <v>61</v>
       </c>
-      <c r="N26" s="155" t="s">
+      <c r="N26" s="103" t="s">
         <v>64</v>
       </c>
-      <c r="O26" s="155" t="s">
+      <c r="O26" s="103" t="s">
         <v>75</v>
       </c>
-      <c r="P26" s="155" t="s">
+      <c r="P26" s="103" t="s">
         <v>66</v>
       </c>
-      <c r="Q26" s="155" t="s">
+      <c r="Q26" s="103" t="s">
         <v>67</v>
       </c>
       <c r="R26" s="9"/>
@@ -15109,22 +15125,22 @@
     </row>
     <row r="27" spans="1:32" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="7"/>
-      <c r="B27" s="158"/>
-      <c r="C27" s="158"/>
-      <c r="D27" s="142"/>
-      <c r="E27" s="142"/>
-      <c r="F27" s="144"/>
-      <c r="G27" s="154"/>
-      <c r="H27" s="154"/>
-      <c r="I27" s="169"/>
-      <c r="J27" s="169"/>
-      <c r="K27" s="156"/>
-      <c r="L27" s="156"/>
-      <c r="M27" s="156"/>
-      <c r="N27" s="156"/>
-      <c r="O27" s="156"/>
-      <c r="P27" s="156"/>
-      <c r="Q27" s="156"/>
+      <c r="B27" s="127"/>
+      <c r="C27" s="127"/>
+      <c r="D27" s="135"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="137"/>
+      <c r="G27" s="125"/>
+      <c r="H27" s="125"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="104"/>
+      <c r="L27" s="104"/>
+      <c r="M27" s="104"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="104"/>
+      <c r="P27" s="104"/>
+      <c r="Q27" s="104"/>
       <c r="R27" s="7"/>
       <c r="S27" s="7"/>
       <c r="T27" s="7"/>
@@ -15146,35 +15162,35 @@
       <c r="B28" s="47" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="172" t="s">
         <v>80</v>
       </c>
       <c r="D28" s="48">
-        <v>2.1705920000000001</v>
+        <v>-5.8280000000154555</v>
       </c>
       <c r="E28" s="48">
-        <v>2.2538339999999999</v>
+        <v>-8.7680000000219867</v>
       </c>
       <c r="F28" s="58">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="G28" s="154"/>
-      <c r="H28" s="154"/>
+      <c r="G28" s="125"/>
+      <c r="H28" s="125"/>
       <c r="I28" s="55">
         <f t="shared" ref="I28:I47" si="1">IF(D28=0,"",LOG($K$15*10^D28+$K$16*10^E28+$K$14))</f>
-        <v>0.25627880917317125</v>
+        <v>-2.3659514487121207E-3</v>
       </c>
       <c r="J28" s="55">
         <f t="shared" ref="J28:J47" si="2">IF(D28=0,"",LOG($K$21*10^D28+$K$22*10^E28+$K$20))</f>
-        <v>1.3139022832264318</v>
+        <v>-5.8715991786462737E-2</v>
       </c>
       <c r="K28" s="56">
         <f t="shared" ref="K28:K47" si="3">IF(D28=0,"",1/(1+10^D28*$J$15/$J$14+10^E28*$J$16/$J$14+10^J28*$J$19/$J$14))</f>
-        <v>0.55125841993906499</v>
+        <v>0.99999999211710799</v>
       </c>
       <c r="L28" s="56">
         <f t="shared" ref="L28:L47" si="4">IF(D28=0,"",1/(1+10^I28/10^J28*$J$13/$J$19))</f>
-        <v>6.9384991713183457E-37</v>
+        <v>5.3369363876718716E-38</v>
       </c>
       <c r="M28" s="56">
         <f t="shared" ref="M28:M47" si="5">IF(D28=0,"",1-L28)</f>
@@ -15182,23 +15198,23 @@
       </c>
       <c r="N28" s="56">
         <f t="shared" ref="N28:N47" si="6">IF(D28=0,"",1/(1/10^E28*$J$20/$J$22+10^D28/10^E28*$J$21/$J$22+10^I28/10^E28*$J$13/$J$22+1))</f>
-        <v>1.9273197866076895E-37</v>
+        <v>3.3247924575537384E-48</v>
       </c>
       <c r="O28" s="57">
         <f t="shared" ref="O28:O47" si="7">IF(D28=0,"",F28*K28*$J$7/$J$14)</f>
-        <v>5.5426976758636183E-6</v>
+        <v>1.0054626708076059E-5</v>
       </c>
       <c r="P28" s="57">
         <f t="shared" ref="P28:P47" si="8">IF(D28=0,"",O28*10^J28)</f>
-        <v>1.1418879080693878E-4</v>
+        <v>8.7831431218000835E-6</v>
       </c>
       <c r="Q28" s="57">
         <f t="shared" ref="Q28:Q47" si="9">IF(D28=0,"",F28*N28*$J$7/$J$22)</f>
-        <v>9.9438643411809378E-4</v>
+        <v>1.715402155378051E-14</v>
       </c>
       <c r="R28" s="9">
         <f>O28/F28</f>
-        <v>0.55426976758636182</v>
+        <v>1.0054626708076058</v>
       </c>
       <c r="S28" s="11"/>
       <c r="T28" s="7"/>
@@ -15217,54 +15233,60 @@
     </row>
     <row r="29" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A29" s="7"/>
-      <c r="B29" s="171" t="s">
+      <c r="B29" s="87" t="s">
         <v>81</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="172" t="s">
         <v>82</v>
       </c>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="154"/>
-      <c r="H29" s="154"/>
-      <c r="I29" s="55" t="str">
+      <c r="D29" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E29" s="48">
+        <v>-4.1624004386372073</v>
+      </c>
+      <c r="F29" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G29" s="125"/>
+      <c r="H29" s="125"/>
+      <c r="I29" s="55" t="e">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J29" s="55" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J29" s="55" t="e">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K29" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K29" s="56" t="e">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L29" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L29" s="56" t="e">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M29" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M29" s="56" t="e">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N29" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N29" s="56" t="e">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O29" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O29" s="57" t="e">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P29" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P29" s="57" t="e">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q29" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q29" s="57" t="e">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R29" s="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R29" s="9"/>
       <c r="S29" s="7"/>
       <c r="T29" s="7"/>
       <c r="U29" s="7"/>
@@ -15282,54 +15304,63 @@
     </row>
     <row r="30" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A30" s="7"/>
-      <c r="B30" s="171" t="s">
+      <c r="B30" s="87" t="s">
         <v>83</v>
       </c>
-      <c r="C30" s="47" t="s">
+      <c r="C30" s="172" t="s">
         <v>84</v>
       </c>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="154"/>
-      <c r="H30" s="154"/>
-      <c r="I30" s="55" t="str">
+      <c r="D30" s="48">
+        <v>4.54</v>
+      </c>
+      <c r="E30" s="48">
+        <v>4.25</v>
+      </c>
+      <c r="F30" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G30" s="125"/>
+      <c r="H30" s="125"/>
+      <c r="I30" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J30" s="55" t="str">
+        <v>2.2712020680003291</v>
+      </c>
+      <c r="J30" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K30" s="86" t="str">
+        <v>3.5851053732977261</v>
+      </c>
+      <c r="K30" s="86">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L30" s="56" t="str">
+        <v>5.3263779155623848E-3</v>
+      </c>
+      <c r="L30" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M30" s="56" t="str">
+        <v>1.251830048507499E-36</v>
+      </c>
+      <c r="M30" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N30" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N30" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O30" s="57" t="str">
+        <v>1.845850490243716E-37</v>
+      </c>
+      <c r="O30" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P30" s="57" t="str">
+        <v>5.3554742069286285E-8</v>
+      </c>
+      <c r="P30" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q30" s="57" t="str">
+        <v>2.0601711696638101E-4</v>
+      </c>
+      <c r="Q30" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R30" s="7"/>
+        <v>9.5235295131757089E-4</v>
+      </c>
+      <c r="R30" s="9">
+        <f t="shared" ref="R29:R55" si="10">O30/F30</f>
+        <v>5.3554742069286277E-3</v>
+      </c>
       <c r="S30" s="7"/>
       <c r="T30" s="7"/>
       <c r="U30" s="7"/>
@@ -15350,51 +15381,60 @@
       <c r="B31" s="47" t="s">
         <v>85</v>
       </c>
-      <c r="C31" s="47" t="s">
+      <c r="C31" s="172" t="s">
         <v>86</v>
       </c>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="154"/>
-      <c r="H31" s="154"/>
-      <c r="I31" s="55" t="str">
+      <c r="D31" s="48">
+        <v>2.83</v>
+      </c>
+      <c r="E31" s="48">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="F31" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G31" s="125"/>
+      <c r="H31" s="125"/>
+      <c r="I31" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J31" s="55" t="str">
+        <v>0.6622271705464875</v>
+      </c>
+      <c r="J31" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K31" s="56" t="str">
+        <v>1.8541141953967648</v>
+      </c>
+      <c r="K31" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L31" s="56" t="str">
+        <v>0.21647456448582855</v>
+      </c>
+      <c r="L31" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M31" s="56" t="str">
+        <v>9.4521170606212484E-37</v>
+      </c>
+      <c r="M31" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N31" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N31" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O31" s="57" t="str">
+        <v>8.8139669702552078E-38</v>
+      </c>
+      <c r="O31" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P31" s="57" t="str">
+        <v>2.1765709548560182E-6</v>
+      </c>
+      <c r="P31" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q31" s="57" t="str">
+        <v>1.5555609232895538E-4</v>
+      </c>
+      <c r="Q31" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R31" s="7"/>
+        <v>4.5475012745099612E-4</v>
+      </c>
+      <c r="R31" s="9">
+        <f t="shared" si="10"/>
+        <v>0.2176570954856018</v>
+      </c>
       <c r="S31" s="7"/>
       <c r="T31" s="7"/>
       <c r="U31" s="7"/>
@@ -15415,51 +15455,57 @@
       <c r="B32" s="47" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="47" t="s">
+      <c r="C32" s="172" t="s">
         <v>88</v>
       </c>
-      <c r="D32" s="48"/>
-      <c r="E32" s="48"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="154"/>
-      <c r="H32" s="154"/>
-      <c r="I32" s="55" t="str">
+      <c r="D32" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E32" s="48">
+        <v>1.7</v>
+      </c>
+      <c r="F32" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G32" s="125"/>
+      <c r="H32" s="125"/>
+      <c r="I32" s="55" t="e">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J32" s="55" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J32" s="55" t="e">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K32" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K32" s="56" t="e">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L32" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L32" s="56" t="e">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M32" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M32" s="56" t="e">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N32" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N32" s="56" t="e">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O32" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O32" s="57" t="e">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P32" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P32" s="57" t="e">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q32" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q32" s="57" t="e">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R32" s="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R32" s="9"/>
       <c r="S32" s="7"/>
       <c r="T32" s="7"/>
       <c r="U32" s="7"/>
@@ -15480,51 +15526,60 @@
       <c r="B33" s="47" t="s">
         <v>89</v>
       </c>
-      <c r="C33" s="47" t="s">
+      <c r="C33" s="172" t="s">
         <v>90</v>
       </c>
-      <c r="D33" s="48"/>
-      <c r="E33" s="48"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="154"/>
-      <c r="H33" s="154"/>
-      <c r="I33" s="55" t="str">
+      <c r="D33" s="48">
+        <v>4.2</v>
+      </c>
+      <c r="E33" s="48">
+        <v>3.52</v>
+      </c>
+      <c r="F33" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G33" s="125"/>
+      <c r="H33" s="125"/>
+      <c r="I33" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J33" s="55" t="str">
+        <v>1.9301000175519432</v>
+      </c>
+      <c r="J33" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K33" s="56" t="str">
+        <v>3.2055222324281836</v>
+      </c>
+      <c r="K33" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L33" s="56" t="str">
+        <v>1.1682452599142133E-2</v>
+      </c>
+      <c r="L33" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M33" s="56" t="str">
+        <v>1.1456825057263878E-36</v>
+      </c>
+      <c r="M33" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N33" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N33" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O33" s="57" t="str">
+        <v>7.5387366374085818E-38</v>
+      </c>
+      <c r="O33" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P33" s="57" t="str">
+        <v>1.1746270084511284E-7</v>
+      </c>
+      <c r="P33" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q33" s="57" t="str">
+        <v>1.8854812366101773E-4</v>
+      </c>
+      <c r="Q33" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R33" s="7"/>
+        <v>3.8895555863216285E-4</v>
+      </c>
+      <c r="R33" s="9">
+        <f t="shared" si="10"/>
+        <v>1.1746270084511283E-2</v>
+      </c>
       <c r="S33" s="7"/>
       <c r="T33" s="7"/>
       <c r="U33" s="7"/>
@@ -15545,51 +15600,60 @@
       <c r="B34" s="47" t="s">
         <v>91</v>
       </c>
-      <c r="C34" s="47" t="s">
+      <c r="C34" s="172" t="s">
         <v>92</v>
       </c>
-      <c r="D34" s="48"/>
-      <c r="E34" s="48"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="154"/>
-      <c r="H34" s="154"/>
-      <c r="I34" s="55" t="str">
+      <c r="D34" s="48">
+        <v>3.44</v>
+      </c>
+      <c r="E34" s="48">
+        <v>-2.9403004386372071</v>
+      </c>
+      <c r="F34" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G34" s="125"/>
+      <c r="H34" s="125"/>
+      <c r="I34" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J34" s="55" t="str">
+        <v>1.1910561641560324</v>
+      </c>
+      <c r="J34" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K34" s="56" t="str">
+        <v>2.4171627270762603</v>
+      </c>
+      <c r="K34" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L34" s="56" t="str">
+        <v>6.405866461130072E-2</v>
+      </c>
+      <c r="L34" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M34" s="56" t="str">
+        <v>1.0227008799512198E-36</v>
+      </c>
+      <c r="M34" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N34" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N34" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O34" s="57" t="str">
+        <v>1.4323263661021073E-43</v>
+      </c>
+      <c r="O34" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P34" s="57" t="str">
+        <v>6.4408596516173101E-7</v>
+      </c>
+      <c r="P34" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q34" s="57" t="str">
+        <v>1.6830869897853311E-4</v>
+      </c>
+      <c r="Q34" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R34" s="7"/>
+        <v>7.3899822830569971E-10</v>
+      </c>
+      <c r="R34" s="9">
+        <f t="shared" si="10"/>
+        <v>6.4408596516173089E-2</v>
+      </c>
       <c r="S34" s="7"/>
       <c r="T34" s="7"/>
       <c r="U34" s="7"/>
@@ -15610,51 +15674,60 @@
       <c r="B35" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="C35" s="47" t="s">
+      <c r="C35" s="172" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="48"/>
-      <c r="E35" s="48"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="154"/>
-      <c r="H35" s="154"/>
-      <c r="I35" s="55" t="str">
+      <c r="D35" s="48">
+        <v>4.49</v>
+      </c>
+      <c r="E35" s="48">
+        <v>-1.7182004386372074</v>
+      </c>
+      <c r="F35" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G35" s="125"/>
+      <c r="H35" s="125"/>
+      <c r="I35" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J35" s="55" t="str">
+        <v>2.2149459403306029</v>
+      </c>
+      <c r="J35" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K35" s="56" t="str">
+        <v>3.4658383349980912</v>
+      </c>
+      <c r="K35" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L35" s="56" t="str">
+        <v>6.0630074907209218E-3</v>
+      </c>
+      <c r="L35" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M35" s="56" t="str">
+        <v>1.0827656294306751E-36</v>
+      </c>
+      <c r="M35" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N35" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N35" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O35" s="57" t="str">
+        <v>2.2607482860836916E-43</v>
+      </c>
+      <c r="O35" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P35" s="57" t="str">
+        <v>6.096127752801895E-8</v>
+      </c>
+      <c r="P35" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q35" s="57" t="str">
+        <v>1.7819372013920811E-4</v>
+      </c>
+      <c r="Q35" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R35" s="7"/>
+        <v>1.16641641011438E-9</v>
+      </c>
+      <c r="R35" s="9">
+        <f t="shared" si="10"/>
+        <v>6.0961277528018944E-3</v>
+      </c>
       <c r="S35" s="7"/>
       <c r="T35" s="7"/>
       <c r="U35" s="7"/>
@@ -15675,51 +15748,60 @@
       <c r="B36" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="C36" s="47" t="s">
+      <c r="C36" s="172" t="s">
         <v>96</v>
       </c>
-      <c r="D36" s="48"/>
-      <c r="E36" s="48"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="154"/>
-      <c r="H36" s="154"/>
-      <c r="I36" s="55" t="str">
+      <c r="D36" s="48">
+        <v>5.17</v>
+      </c>
+      <c r="E36" s="48">
+        <v>4.54</v>
+      </c>
+      <c r="F36" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G36" s="125"/>
+      <c r="H36" s="125"/>
+      <c r="I36" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J36" s="55" t="str">
+        <v>2.8958731392461319</v>
+      </c>
+      <c r="J36" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K36" s="86" t="str">
+        <v>4.1787858561368472</v>
+      </c>
+      <c r="K36" s="86">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L36" s="56" t="str">
+        <v>1.2640402580400185E-3</v>
+      </c>
+      <c r="L36" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M36" s="56" t="str">
+        <v>1.1656140766551229E-36</v>
+      </c>
+      <c r="M36" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N36" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N36" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O36" s="57" t="str">
+        <v>8.5413289879180715E-38</v>
+      </c>
+      <c r="O36" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P36" s="57" t="str">
+        <v>1.2709453038759766E-8</v>
+      </c>
+      <c r="P36" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q36" s="57" t="str">
+        <v>1.9182831715393195E-4</v>
+      </c>
+      <c r="Q36" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R36" s="7"/>
+        <v>4.4068357176339231E-4</v>
+      </c>
+      <c r="R36" s="9">
+        <f t="shared" si="10"/>
+        <v>1.2709453038759766E-3</v>
+      </c>
       <c r="S36" s="7"/>
       <c r="T36" s="7"/>
       <c r="U36" s="7"/>
@@ -15740,51 +15822,60 @@
       <c r="B37" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="C37" s="47" t="s">
+      <c r="C37" s="172" t="s">
         <v>98</v>
       </c>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="154"/>
-      <c r="H37" s="154"/>
-      <c r="I37" s="55" t="str">
+      <c r="D37" s="48">
+        <v>4.76</v>
+      </c>
+      <c r="E37" s="48">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F37" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G37" s="125"/>
+      <c r="H37" s="125"/>
+      <c r="I37" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J37" s="55" t="str">
+        <v>2.5007629060769907</v>
+      </c>
+      <c r="J37" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K37" s="56" t="str">
+        <v>3.8986308185716281</v>
+      </c>
+      <c r="K37" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L37" s="56" t="str">
+        <v>3.1395770014054033E-3</v>
+      </c>
+      <c r="L37" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M37" s="56" t="str">
+        <v>1.5188328413009652E-36</v>
+      </c>
+      <c r="M37" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N37" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N37" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O37" s="57" t="str">
+        <v>4.7493664843015257E-37</v>
+      </c>
+      <c r="O37" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P37" s="57" t="str">
+        <v>3.156727501923353E-8</v>
+      </c>
+      <c r="P37" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q37" s="57" t="str">
+        <v>2.4995850154878855E-4</v>
+      </c>
+      <c r="Q37" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R37" s="7"/>
+        <v>2.4504006213504929E-3</v>
+      </c>
+      <c r="R37" s="9">
+        <f t="shared" si="10"/>
+        <v>3.1567275019233529E-3</v>
+      </c>
       <c r="S37" s="7"/>
       <c r="T37" s="7"/>
       <c r="U37" s="7"/>
@@ -15805,51 +15896,60 @@
       <c r="B38" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="47" t="s">
+      <c r="C38" s="172" t="s">
         <v>100</v>
       </c>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="154"/>
-      <c r="H38" s="154"/>
-      <c r="I38" s="55" t="str">
+      <c r="D38" s="48">
+        <v>3.93</v>
+      </c>
+      <c r="E38" s="48">
+        <v>2.91</v>
+      </c>
+      <c r="F38" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G38" s="125"/>
+      <c r="H38" s="125"/>
+      <c r="I38" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J38" s="55" t="str">
+        <v>1.6630242206595924</v>
+      </c>
+      <c r="J38" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K38" s="56" t="str">
+        <v>2.9199347073802309</v>
+      </c>
+      <c r="K38" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L38" s="56" t="str">
+        <v>2.1607763832193882E-2</v>
+      </c>
+      <c r="L38" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M38" s="56" t="str">
+        <v>1.0978741345922021E-36</v>
+      </c>
+      <c r="M38" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N38" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N38" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O38" s="57" t="str">
+        <v>3.4227436118757005E-38</v>
+      </c>
+      <c r="O38" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P38" s="57" t="str">
+        <v>2.1725800104159784E-7</v>
+      </c>
+      <c r="P38" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q38" s="57" t="str">
+        <v>1.8068016842247194E-4</v>
+      </c>
+      <c r="Q38" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R38" s="7"/>
+        <v>1.7659393312742237E-4</v>
+      </c>
+      <c r="R38" s="9">
+        <f t="shared" si="10"/>
+        <v>2.1725800104159781E-2</v>
+      </c>
       <c r="S38" s="7"/>
       <c r="T38" s="7"/>
       <c r="U38" s="7"/>
@@ -15870,51 +15970,57 @@
       <c r="B39" s="47" t="s">
         <v>101</v>
       </c>
-      <c r="C39" s="47" t="s">
+      <c r="C39" s="172" t="s">
         <v>102</v>
       </c>
-      <c r="D39" s="48"/>
-      <c r="E39" s="48"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="154"/>
-      <c r="H39" s="154"/>
-      <c r="I39" s="55" t="str">
+      <c r="D39" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E39" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="F39" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G39" s="125"/>
+      <c r="H39" s="125"/>
+      <c r="I39" s="55" t="e">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J39" s="55" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J39" s="55" t="e">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K39" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K39" s="56" t="e">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L39" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L39" s="56" t="e">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M39" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M39" s="56" t="e">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N39" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N39" s="56" t="e">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O39" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O39" s="57" t="e">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P39" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P39" s="57" t="e">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q39" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q39" s="57" t="e">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R39" s="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R39" s="9"/>
       <c r="S39" s="7"/>
       <c r="T39" s="7"/>
       <c r="U39" s="7"/>
@@ -15935,51 +16041,60 @@
       <c r="B40" s="47" t="s">
         <v>103</v>
       </c>
-      <c r="C40" s="47" t="s">
+      <c r="C40" s="172" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="48"/>
-      <c r="E40" s="48"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="154"/>
-      <c r="H40" s="154"/>
-      <c r="I40" s="55" t="str">
+      <c r="D40" s="48">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="E40" s="48">
+        <v>4.13</v>
+      </c>
+      <c r="F40" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G40" s="125"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J40" s="55" t="str">
+        <v>2.3385486683944654</v>
+      </c>
+      <c r="J40" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K40" s="56" t="str">
+        <v>3.6317841111510814</v>
+      </c>
+      <c r="K40" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L40" s="56" t="str">
+        <v>4.5612657578140894E-3</v>
+      </c>
+      <c r="L40" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M40" s="56" t="str">
+        <v>1.1936513937058188E-36</v>
+      </c>
+      <c r="M40" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N40" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N40" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O40" s="57" t="str">
+        <v>1.1990848637437677E-37</v>
+      </c>
+      <c r="O40" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P40" s="57" t="str">
+        <v>4.5861824872674131E-8</v>
+      </c>
+      <c r="P40" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q40" s="57" t="str">
+        <v>1.9644249559863669E-4</v>
+      </c>
+      <c r="Q40" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R40" s="7"/>
+        <v>6.1865899481156105E-4</v>
+      </c>
+      <c r="R40" s="9">
+        <f t="shared" si="10"/>
+        <v>4.5861824872674125E-3</v>
+      </c>
       <c r="S40" s="7"/>
       <c r="T40" s="7"/>
       <c r="U40" s="7"/>
@@ -16000,51 +16115,60 @@
       <c r="B41" s="47" t="s">
         <v>105</v>
       </c>
-      <c r="C41" s="47" t="s">
+      <c r="C41" s="172" t="s">
         <v>106</v>
       </c>
-      <c r="D41" s="48"/>
-      <c r="E41" s="48"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="154"/>
-      <c r="H41" s="154"/>
-      <c r="I41" s="55" t="str">
+      <c r="D41" s="48">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="E41" s="48">
+        <v>4.82</v>
+      </c>
+      <c r="F41" s="58">
+        <v>1.0000000000000001E-5</v>
+      </c>
+      <c r="G41" s="125"/>
+      <c r="H41" s="125"/>
+      <c r="I41" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J41" s="55" t="str">
+        <v>2.5465607077581862</v>
+      </c>
+      <c r="J41" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K41" s="56" t="str">
+        <v>3.9145356619532561</v>
+      </c>
+      <c r="K41" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L41" s="56" t="str">
+        <v>2.8253570400599884E-3</v>
+      </c>
+      <c r="L41" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M41" s="56" t="str">
+        <v>1.4178066888089344E-36</v>
+      </c>
+      <c r="M41" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N41" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N41" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O41" s="57" t="str">
+        <v>3.6377921501801176E-37</v>
+      </c>
+      <c r="O41" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P41" s="57" t="str">
+        <v>2.840791057877437E-8</v>
+      </c>
+      <c r="P41" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q41" s="57" t="str">
+        <v>2.3333234954083136E-4</v>
+      </c>
+      <c r="Q41" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R41" s="7"/>
+        <v>1.876892039098193E-3</v>
+      </c>
+      <c r="R41" s="9">
+        <f t="shared" si="10"/>
+        <v>2.8407910578774368E-3</v>
+      </c>
       <c r="S41" s="7"/>
       <c r="T41" s="7"/>
       <c r="U41" s="7"/>
@@ -16069,31 +16193,31 @@
         <v>80</v>
       </c>
       <c r="D42" s="48">
-        <v>2.1705920000000001</v>
+        <v>-5.8280000000154555</v>
       </c>
       <c r="E42" s="48">
-        <v>2.2538339999999999</v>
+        <v>-8.7680000000219867</v>
       </c>
       <c r="F42" s="58">
         <v>1E-4</v>
       </c>
-      <c r="G42" s="154"/>
-      <c r="H42" s="154"/>
+      <c r="G42" s="125"/>
+      <c r="H42" s="125"/>
       <c r="I42" s="55">
         <f t="shared" si="1"/>
-        <v>0.25627880917317125</v>
+        <v>-2.3659514487121207E-3</v>
       </c>
       <c r="J42" s="55">
         <f t="shared" si="2"/>
-        <v>1.3139022832264318</v>
+        <v>-5.8715991786462737E-2</v>
       </c>
       <c r="K42" s="56">
         <f t="shared" si="3"/>
-        <v>0.55125841993906499</v>
+        <v>0.99999999211710799</v>
       </c>
       <c r="L42" s="56">
         <f t="shared" si="4"/>
-        <v>6.9384991713183457E-37</v>
+        <v>5.3369363876718716E-38</v>
       </c>
       <c r="M42" s="56">
         <f t="shared" si="5"/>
@@ -16101,23 +16225,23 @@
       </c>
       <c r="N42" s="56">
         <f t="shared" si="6"/>
-        <v>1.9273197866076895E-37</v>
+        <v>3.3247924575537384E-48</v>
       </c>
       <c r="O42" s="57">
         <f t="shared" si="7"/>
-        <v>5.5426976758636173E-5</v>
+        <v>1.0054626708076057E-4</v>
       </c>
       <c r="P42" s="57">
         <f t="shared" si="8"/>
-        <v>1.1418879080693875E-3</v>
+        <v>8.7831431218000807E-5</v>
       </c>
       <c r="Q42" s="57">
         <f t="shared" si="9"/>
-        <v>9.9438643411809378E-3</v>
+        <v>1.7154021553780509E-13</v>
       </c>
       <c r="R42" s="9">
-        <f>O42/F42</f>
-        <v>0.55426976758636171</v>
+        <f t="shared" si="10"/>
+        <v>1.0054626708076055</v>
       </c>
       <c r="S42" s="7"/>
       <c r="T42" s="7"/>
@@ -16136,54 +16260,60 @@
     </row>
     <row r="43" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A43" s="7"/>
-      <c r="B43" s="171" t="s">
+      <c r="B43" s="87" t="s">
         <v>81</v>
       </c>
       <c r="C43" s="47" t="s">
         <v>82</v>
       </c>
-      <c r="D43" s="48"/>
-      <c r="E43" s="48"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="154"/>
-      <c r="H43" s="154"/>
-      <c r="I43" s="55" t="str">
+      <c r="D43" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E43" s="48">
+        <v>-4.1624004386372073</v>
+      </c>
+      <c r="F43" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G43" s="125"/>
+      <c r="H43" s="125"/>
+      <c r="I43" s="55" t="e">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J43" s="55" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J43" s="55" t="e">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K43" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K43" s="56" t="e">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L43" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L43" s="56" t="e">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M43" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M43" s="56" t="e">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N43" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N43" s="56" t="e">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O43" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O43" s="57" t="e">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P43" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P43" s="57" t="e">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q43" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q43" s="57" t="e">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R43" s="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R43" s="9"/>
       <c r="S43" s="7"/>
       <c r="T43" s="7"/>
       <c r="U43" s="7"/>
@@ -16201,54 +16331,63 @@
     </row>
     <row r="44" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A44" s="7"/>
-      <c r="B44" s="171" t="s">
+      <c r="B44" s="87" t="s">
         <v>83</v>
       </c>
       <c r="C44" s="47" t="s">
         <v>84</v>
       </c>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="154"/>
-      <c r="H44" s="154"/>
-      <c r="I44" s="55" t="str">
+      <c r="D44" s="48">
+        <v>4.54</v>
+      </c>
+      <c r="E44" s="48">
+        <v>4.25</v>
+      </c>
+      <c r="F44" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G44" s="125"/>
+      <c r="H44" s="125"/>
+      <c r="I44" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J44" s="55" t="str">
+        <v>2.2712020680003291</v>
+      </c>
+      <c r="J44" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K44" s="56" t="str">
+        <v>3.5851053732977261</v>
+      </c>
+      <c r="K44" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L44" s="56" t="str">
+        <v>5.3263779155623848E-3</v>
+      </c>
+      <c r="L44" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M44" s="56" t="str">
+        <v>1.251830048507499E-36</v>
+      </c>
+      <c r="M44" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N44" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N44" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O44" s="57" t="str">
+        <v>1.845850490243716E-37</v>
+      </c>
+      <c r="O44" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P44" s="57" t="str">
+        <v>5.3554742069286275E-7</v>
+      </c>
+      <c r="P44" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q44" s="57" t="str">
+        <v>2.0601711696638099E-3</v>
+      </c>
+      <c r="Q44" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R44" s="7"/>
+        <v>9.5235295131757096E-3</v>
+      </c>
+      <c r="R44" s="9">
+        <f t="shared" si="10"/>
+        <v>5.3554742069286268E-3</v>
+      </c>
       <c r="S44" s="7"/>
       <c r="T44" s="7"/>
       <c r="U44" s="7"/>
@@ -16272,48 +16411,57 @@
       <c r="C45" s="47" t="s">
         <v>86</v>
       </c>
-      <c r="D45" s="48"/>
-      <c r="E45" s="48"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="154"/>
-      <c r="H45" s="154"/>
-      <c r="I45" s="55" t="str">
+      <c r="D45" s="48">
+        <v>2.83</v>
+      </c>
+      <c r="E45" s="48">
+        <v>2.3199999999999998</v>
+      </c>
+      <c r="F45" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G45" s="125"/>
+      <c r="H45" s="125"/>
+      <c r="I45" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J45" s="55" t="str">
+        <v>0.6622271705464875</v>
+      </c>
+      <c r="J45" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K45" s="56" t="str">
+        <v>1.8541141953967648</v>
+      </c>
+      <c r="K45" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L45" s="56" t="str">
+        <v>0.21647456448582855</v>
+      </c>
+      <c r="L45" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M45" s="56" t="str">
+        <v>9.4521170606212484E-37</v>
+      </c>
+      <c r="M45" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N45" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N45" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O45" s="57" t="str">
+        <v>8.8139669702552078E-38</v>
+      </c>
+      <c r="O45" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P45" s="57" t="str">
+        <v>2.1765709548560185E-5</v>
+      </c>
+      <c r="P45" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q45" s="57" t="str">
+        <v>1.5555609232895541E-3</v>
+      </c>
+      <c r="Q45" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R45" s="7"/>
+        <v>4.5475012745099614E-3</v>
+      </c>
+      <c r="R45" s="9">
+        <f t="shared" si="10"/>
+        <v>0.21765709548560183</v>
+      </c>
       <c r="S45" s="7"/>
       <c r="T45" s="7"/>
       <c r="U45" s="7"/>
@@ -16337,48 +16485,57 @@
       <c r="C46" s="47" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="154"/>
-      <c r="H46" s="154"/>
-      <c r="I46" s="55" t="str">
+      <c r="D46" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E46" s="48">
+        <v>1.7</v>
+      </c>
+      <c r="F46" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G46" s="125"/>
+      <c r="H46" s="125"/>
+      <c r="I46" s="55" t="e">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J46" s="55" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J46" s="55" t="e">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K46" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K46" s="56" t="e">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L46" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L46" s="56" t="e">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M46" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M46" s="56" t="e">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N46" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N46" s="56" t="e">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O46" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O46" s="57" t="e">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P46" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P46" s="57" t="e">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q46" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q46" s="57" t="e">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R46" s="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R46" s="9" t="e">
+        <f t="shared" si="10"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="S46" s="7"/>
       <c r="T46" s="7"/>
       <c r="U46" s="7"/>
@@ -16402,48 +16559,57 @@
       <c r="C47" s="47" t="s">
         <v>90</v>
       </c>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="154"/>
-      <c r="H47" s="154"/>
-      <c r="I47" s="55" t="str">
+      <c r="D47" s="48">
+        <v>4.2</v>
+      </c>
+      <c r="E47" s="48">
+        <v>3.52</v>
+      </c>
+      <c r="F47" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G47" s="125"/>
+      <c r="H47" s="125"/>
+      <c r="I47" s="55">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="J47" s="55" t="str">
+        <v>1.9301000175519432</v>
+      </c>
+      <c r="J47" s="55">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="K47" s="56" t="str">
+        <v>3.2055222324281836</v>
+      </c>
+      <c r="K47" s="56">
         <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="L47" s="56" t="str">
+        <v>1.1682452599142133E-2</v>
+      </c>
+      <c r="L47" s="56">
         <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="M47" s="56" t="str">
+        <v>1.1456825057263878E-36</v>
+      </c>
+      <c r="M47" s="56">
         <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="N47" s="56" t="str">
+        <v>1</v>
+      </c>
+      <c r="N47" s="56">
         <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="O47" s="57" t="str">
+        <v>7.5387366374085818E-38</v>
+      </c>
+      <c r="O47" s="57">
         <f t="shared" si="7"/>
-        <v/>
-      </c>
-      <c r="P47" s="57" t="str">
+        <v>1.1746270084511283E-6</v>
+      </c>
+      <c r="P47" s="57">
         <f t="shared" si="8"/>
-        <v/>
-      </c>
-      <c r="Q47" s="57" t="str">
+        <v>1.8854812366101772E-3</v>
+      </c>
+      <c r="Q47" s="57">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="R47" s="7"/>
+        <v>3.8895555863216287E-3</v>
+      </c>
+      <c r="R47" s="9">
+        <f t="shared" si="10"/>
+        <v>1.1746270084511283E-2</v>
+      </c>
       <c r="S47" s="7"/>
       <c r="T47" s="7"/>
       <c r="U47" s="7"/>
@@ -16467,48 +16633,57 @@
       <c r="C48" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="D48" s="48"/>
-      <c r="E48" s="48"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="154"/>
-      <c r="H48" s="154"/>
-      <c r="I48" s="83" t="str">
-        <f t="shared" ref="I48:I50" si="10">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
-        <v/>
-      </c>
-      <c r="J48" s="83" t="str">
-        <f t="shared" ref="J48:J50" si="11">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
-        <v/>
-      </c>
-      <c r="K48" s="84" t="str">
-        <f t="shared" ref="K48:K50" si="12">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
-        <v/>
-      </c>
-      <c r="L48" s="84" t="str">
-        <f t="shared" ref="L48:L50" si="13">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
-        <v/>
-      </c>
-      <c r="M48" s="84" t="str">
-        <f t="shared" ref="M48:M92" si="14">IF(D48=0,"",1-L48)</f>
-        <v/>
-      </c>
-      <c r="N48" s="84" t="str">
-        <f t="shared" ref="N48:N50" si="15">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
-        <v/>
-      </c>
-      <c r="O48" s="85" t="str">
-        <f t="shared" ref="O48:O92" si="16">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
-        <v/>
-      </c>
-      <c r="P48" s="85" t="str">
-        <f t="shared" ref="P48:P50" si="17">IF(D48=0,"",O48*10^J48)</f>
-        <v/>
-      </c>
-      <c r="Q48" s="85" t="str">
-        <f t="shared" ref="Q48:Q50" si="18">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
-        <v/>
-      </c>
-      <c r="R48" s="7"/>
+      <c r="D48" s="48">
+        <v>3.44</v>
+      </c>
+      <c r="E48" s="48">
+        <v>-2.9403004386372071</v>
+      </c>
+      <c r="F48" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G48" s="125"/>
+      <c r="H48" s="125"/>
+      <c r="I48" s="83">
+        <f t="shared" ref="I48:I50" si="11">IF(D48=0,"",LOG($K$15*10^D48+$K$16*10^E48+$K$14))</f>
+        <v>1.1910561641560324</v>
+      </c>
+      <c r="J48" s="83">
+        <f t="shared" ref="J48:J50" si="12">IF(D48=0,"",LOG($K$21*10^D48+$K$22*10^E48+$K$20))</f>
+        <v>2.4171627270762603</v>
+      </c>
+      <c r="K48" s="84">
+        <f t="shared" ref="K48:K50" si="13">IF(D48=0,"",1/(1+10^D48*$J$15/$J$14+10^E48*$J$16/$J$14+10^J48*$J$19/$J$14))</f>
+        <v>6.405866461130072E-2</v>
+      </c>
+      <c r="L48" s="84">
+        <f t="shared" ref="L48:L50" si="14">IF(D48=0,"",1/(1+10^I48/10^J48*$J$13/$J$19))</f>
+        <v>1.0227008799512198E-36</v>
+      </c>
+      <c r="M48" s="84">
+        <f t="shared" ref="M48:M92" si="15">IF(D48=0,"",1-L48)</f>
+        <v>1</v>
+      </c>
+      <c r="N48" s="84">
+        <f t="shared" ref="N48:N50" si="16">IF(D48=0,"",1/(1/10^E48*$J$20/$J$22+10^D48/10^E48*$J$21/$J$22+10^I48/10^E48*$J$13/$J$22+1))</f>
+        <v>1.4323263661021073E-43</v>
+      </c>
+      <c r="O48" s="85">
+        <f t="shared" ref="O48:O92" si="17">IF(D48=0,"",F48*K48*$J$7/$J$14)</f>
+        <v>6.440859651617309E-6</v>
+      </c>
+      <c r="P48" s="85">
+        <f t="shared" ref="P48:P50" si="18">IF(D48=0,"",O48*10^J48)</f>
+        <v>1.6830869897853308E-3</v>
+      </c>
+      <c r="Q48" s="85">
+        <f t="shared" ref="Q48:Q50" si="19">IF(D48=0,"",F48*N48*$J$7/$J$22)</f>
+        <v>7.3899822830569973E-9</v>
+      </c>
+      <c r="R48" s="9">
+        <f t="shared" si="10"/>
+        <v>6.4408596516173089E-2</v>
+      </c>
       <c r="S48" s="7"/>
       <c r="T48" s="7"/>
       <c r="U48" s="7"/>
@@ -16532,48 +16707,57 @@
       <c r="C49" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="D49" s="48"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="154"/>
-      <c r="H49" s="154"/>
-      <c r="I49" s="55" t="str">
+      <c r="D49" s="48">
+        <v>4.49</v>
+      </c>
+      <c r="E49" s="48">
+        <v>-1.7182004386372074</v>
+      </c>
+      <c r="F49" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G49" s="125"/>
+      <c r="H49" s="125"/>
+      <c r="I49" s="55">
+        <f t="shared" si="11"/>
+        <v>2.2149459403306029</v>
+      </c>
+      <c r="J49" s="55">
+        <f t="shared" si="12"/>
+        <v>3.4658383349980912</v>
+      </c>
+      <c r="K49" s="56">
+        <f t="shared" si="13"/>
+        <v>6.0630074907209218E-3</v>
+      </c>
+      <c r="L49" s="56">
+        <f t="shared" si="14"/>
+        <v>1.0827656294306751E-36</v>
+      </c>
+      <c r="M49" s="56">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="N49" s="56">
+        <f t="shared" si="16"/>
+        <v>2.2607482860836916E-43</v>
+      </c>
+      <c r="O49" s="57">
+        <f t="shared" si="17"/>
+        <v>6.0961277528018952E-7</v>
+      </c>
+      <c r="P49" s="57">
+        <f t="shared" si="18"/>
+        <v>1.7819372013920811E-3</v>
+      </c>
+      <c r="Q49" s="57">
+        <f t="shared" si="19"/>
+        <v>1.1664164101143801E-8</v>
+      </c>
+      <c r="R49" s="9">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J49" s="55" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K49" s="56" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="L49" s="56" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="M49" s="56" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="N49" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="O49" s="57" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="P49" s="57" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="Q49" s="57" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="R49" s="7"/>
+        <v>6.0961277528018953E-3</v>
+      </c>
       <c r="S49" s="7"/>
       <c r="T49" s="7"/>
       <c r="U49" s="7"/>
@@ -16597,48 +16781,57 @@
       <c r="C50" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="D50" s="48"/>
-      <c r="E50" s="48"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="154"/>
-      <c r="H50" s="154"/>
-      <c r="I50" s="55" t="str">
+      <c r="D50" s="48">
+        <v>5.17</v>
+      </c>
+      <c r="E50" s="48">
+        <v>4.54</v>
+      </c>
+      <c r="F50" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G50" s="125"/>
+      <c r="H50" s="125"/>
+      <c r="I50" s="55">
+        <f t="shared" si="11"/>
+        <v>2.8958731392461319</v>
+      </c>
+      <c r="J50" s="55">
+        <f t="shared" si="12"/>
+        <v>4.1787858561368472</v>
+      </c>
+      <c r="K50" s="56">
+        <f t="shared" si="13"/>
+        <v>1.2640402580400185E-3</v>
+      </c>
+      <c r="L50" s="56">
+        <f t="shared" si="14"/>
+        <v>1.1656140766551229E-36</v>
+      </c>
+      <c r="M50" s="56">
+        <f t="shared" si="15"/>
+        <v>1</v>
+      </c>
+      <c r="N50" s="56">
+        <f t="shared" si="16"/>
+        <v>8.5413289879180715E-38</v>
+      </c>
+      <c r="O50" s="57">
+        <f t="shared" si="17"/>
+        <v>1.2709453038759767E-7</v>
+      </c>
+      <c r="P50" s="57">
+        <f t="shared" si="18"/>
+        <v>1.9182831715393197E-3</v>
+      </c>
+      <c r="Q50" s="57">
+        <f t="shared" si="19"/>
+        <v>4.4068357176339232E-3</v>
+      </c>
+      <c r="R50" s="9">
         <f t="shared" si="10"/>
-        <v/>
-      </c>
-      <c r="J50" s="55" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="K50" s="56" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-      <c r="L50" s="56" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="M50" s="56" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="N50" s="56" t="str">
-        <f t="shared" si="15"/>
-        <v/>
-      </c>
-      <c r="O50" s="57" t="str">
-        <f t="shared" si="16"/>
-        <v/>
-      </c>
-      <c r="P50" s="57" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="Q50" s="57" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-      <c r="R50" s="7"/>
+        <v>1.2709453038759768E-3</v>
+      </c>
       <c r="S50" s="7"/>
       <c r="T50" s="7"/>
       <c r="U50" s="7"/>
@@ -16662,48 +16855,57 @@
       <c r="C51" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="D51" s="48"/>
-      <c r="E51" s="48"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="154"/>
-      <c r="H51" s="154"/>
-      <c r="I51" s="55" t="str">
-        <f t="shared" ref="I51:I70" si="19">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
-        <v/>
-      </c>
-      <c r="J51" s="55" t="str">
-        <f t="shared" ref="J51:J70" si="20">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
-        <v/>
-      </c>
-      <c r="K51" s="56" t="str">
-        <f t="shared" ref="K51:K70" si="21">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
-        <v/>
-      </c>
-      <c r="L51" s="56" t="str">
-        <f t="shared" ref="L51:L70" si="22">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
-        <v/>
-      </c>
-      <c r="M51" s="56" t="str">
-        <f t="shared" ref="M51:M70" si="23">IF(D51=0,"",1-L51)</f>
-        <v/>
-      </c>
-      <c r="N51" s="56" t="str">
-        <f t="shared" ref="N51:N70" si="24">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
-        <v/>
-      </c>
-      <c r="O51" s="57" t="str">
-        <f t="shared" ref="O51:O70" si="25">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
-        <v/>
-      </c>
-      <c r="P51" s="57" t="str">
-        <f t="shared" ref="P51:P70" si="26">IF(D51=0,"",O51*10^J51)</f>
-        <v/>
-      </c>
-      <c r="Q51" s="57" t="str">
-        <f t="shared" ref="Q51:Q70" si="27">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
-        <v/>
-      </c>
-      <c r="R51" s="7"/>
+      <c r="D51" s="48">
+        <v>4.76</v>
+      </c>
+      <c r="E51" s="48">
+        <v>4.8899999999999997</v>
+      </c>
+      <c r="F51" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G51" s="125"/>
+      <c r="H51" s="125"/>
+      <c r="I51" s="55">
+        <f t="shared" ref="I51:I70" si="20">IF(D51=0,"",LOG($K$15*10^D51+$K$16*10^E51+$K$14))</f>
+        <v>2.5007629060769907</v>
+      </c>
+      <c r="J51" s="55">
+        <f t="shared" ref="J51:J70" si="21">IF(D51=0,"",LOG($K$21*10^D51+$K$22*10^E51+$K$20))</f>
+        <v>3.8986308185716281</v>
+      </c>
+      <c r="K51" s="56">
+        <f t="shared" ref="K51:K70" si="22">IF(D51=0,"",1/(1+10^D51*$J$15/$J$14+10^E51*$J$16/$J$14+10^J51*$J$19/$J$14))</f>
+        <v>3.1395770014054033E-3</v>
+      </c>
+      <c r="L51" s="56">
+        <f t="shared" ref="L51:L70" si="23">IF(D51=0,"",1/(1+10^I51/10^J51*$J$13/$J$19))</f>
+        <v>1.5188328413009652E-36</v>
+      </c>
+      <c r="M51" s="56">
+        <f t="shared" ref="M51:M70" si="24">IF(D51=0,"",1-L51)</f>
+        <v>1</v>
+      </c>
+      <c r="N51" s="56">
+        <f t="shared" ref="N51:N70" si="25">IF(D51=0,"",1/(1/10^E51*$J$20/$J$22+10^D51/10^E51*$J$21/$J$22+10^I51/10^E51*$J$13/$J$22+1))</f>
+        <v>4.7493664843015257E-37</v>
+      </c>
+      <c r="O51" s="57">
+        <f t="shared" ref="O51:O70" si="26">IF(D51=0,"",F51*K51*$J$7/$J$14)</f>
+        <v>3.1567275019233534E-7</v>
+      </c>
+      <c r="P51" s="57">
+        <f t="shared" ref="P51:P70" si="27">IF(D51=0,"",O51*10^J51)</f>
+        <v>2.4995850154878856E-3</v>
+      </c>
+      <c r="Q51" s="57">
+        <f t="shared" ref="Q51:Q70" si="28">IF(D51=0,"",F51*N51*$J$7/$J$22)</f>
+        <v>2.4504006213504927E-2</v>
+      </c>
+      <c r="R51" s="9">
+        <f t="shared" si="10"/>
+        <v>3.1567275019233534E-3</v>
+      </c>
       <c r="S51" s="7"/>
       <c r="T51" s="7"/>
       <c r="U51" s="7"/>
@@ -16727,48 +16929,57 @@
       <c r="C52" s="47" t="s">
         <v>100</v>
       </c>
-      <c r="D52" s="48"/>
-      <c r="E52" s="48"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="154"/>
-      <c r="H52" s="154"/>
-      <c r="I52" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="J52" s="55" t="str">
+      <c r="D52" s="48">
+        <v>3.93</v>
+      </c>
+      <c r="E52" s="48">
+        <v>2.91</v>
+      </c>
+      <c r="F52" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G52" s="125"/>
+      <c r="H52" s="125"/>
+      <c r="I52" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K52" s="56" t="str">
+        <v>1.6630242206595924</v>
+      </c>
+      <c r="J52" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="L52" s="56" t="str">
+        <v>2.9199347073802309</v>
+      </c>
+      <c r="K52" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="M52" s="56" t="str">
+        <v>2.1607763832193882E-2</v>
+      </c>
+      <c r="L52" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N52" s="56" t="str">
+        <v>1.0978741345922021E-36</v>
+      </c>
+      <c r="M52" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="O52" s="57" t="str">
+        <v>1</v>
+      </c>
+      <c r="N52" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="P52" s="57" t="str">
+        <v>3.4227436118757005E-38</v>
+      </c>
+      <c r="O52" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="Q52" s="57" t="str">
+        <v>2.1725800104159782E-6</v>
+      </c>
+      <c r="P52" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="R52" s="7"/>
+        <v>1.806801684224719E-3</v>
+      </c>
+      <c r="Q52" s="57">
+        <f t="shared" si="28"/>
+        <v>1.7659393312742236E-3</v>
+      </c>
+      <c r="R52" s="9">
+        <f t="shared" si="10"/>
+        <v>2.1725800104159781E-2</v>
+      </c>
       <c r="S52" s="7"/>
       <c r="T52" s="7"/>
       <c r="U52" s="7"/>
@@ -16792,48 +17003,57 @@
       <c r="C53" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="D53" s="48"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="154"/>
-      <c r="H53" s="154"/>
-      <c r="I53" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="J53" s="55" t="str">
+      <c r="D53" s="48" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" s="48" t="s">
+        <v>108</v>
+      </c>
+      <c r="F53" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G53" s="125"/>
+      <c r="H53" s="125"/>
+      <c r="I53" s="55" t="e">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K53" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J53" s="55" t="e">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="L53" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K53" s="56" t="e">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="M53" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="L53" s="56" t="e">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N53" s="56" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M53" s="56" t="e">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="O53" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="N53" s="56" t="e">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="P53" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="O53" s="57" t="e">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="Q53" s="57" t="str">
+        <v>#VALUE!</v>
+      </c>
+      <c r="P53" s="57" t="e">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="R53" s="7"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="Q53" s="57" t="e">
+        <f t="shared" si="28"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="R53" s="9" t="e">
+        <f t="shared" si="10"/>
+        <v>#VALUE!</v>
+      </c>
       <c r="S53" s="7"/>
       <c r="T53" s="7"/>
       <c r="U53" s="7"/>
@@ -16857,48 +17077,57 @@
       <c r="C54" s="47" t="s">
         <v>104</v>
       </c>
-      <c r="D54" s="48"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="154"/>
-      <c r="H54" s="154"/>
-      <c r="I54" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="J54" s="55" t="str">
+      <c r="D54" s="48">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="E54" s="48">
+        <v>4.13</v>
+      </c>
+      <c r="F54" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G54" s="125"/>
+      <c r="H54" s="125"/>
+      <c r="I54" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K54" s="56" t="str">
+        <v>2.3385486683944654</v>
+      </c>
+      <c r="J54" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="L54" s="56" t="str">
+        <v>3.6317841111510814</v>
+      </c>
+      <c r="K54" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="M54" s="56" t="str">
+        <v>4.5612657578140894E-3</v>
+      </c>
+      <c r="L54" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N54" s="56" t="str">
+        <v>1.1936513937058188E-36</v>
+      </c>
+      <c r="M54" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="O54" s="57" t="str">
+        <v>1</v>
+      </c>
+      <c r="N54" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="P54" s="57" t="str">
+        <v>1.1990848637437677E-37</v>
+      </c>
+      <c r="O54" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="Q54" s="57" t="str">
+        <v>4.5861824872674136E-7</v>
+      </c>
+      <c r="P54" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="R54" s="7"/>
+        <v>1.9644249559863671E-3</v>
+      </c>
+      <c r="Q54" s="57">
+        <f t="shared" si="28"/>
+        <v>6.1865899481156096E-3</v>
+      </c>
+      <c r="R54" s="9">
+        <f t="shared" si="10"/>
+        <v>4.5861824872674133E-3</v>
+      </c>
       <c r="S54" s="7"/>
       <c r="T54" s="7"/>
       <c r="U54" s="7"/>
@@ -16922,48 +17151,57 @@
       <c r="C55" s="47" t="s">
         <v>106</v>
       </c>
-      <c r="D55" s="48"/>
-      <c r="E55" s="48"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="154"/>
-      <c r="H55" s="154"/>
-      <c r="I55" s="55" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="J55" s="55" t="str">
+      <c r="D55" s="48">
+        <v>4.8099999999999996</v>
+      </c>
+      <c r="E55" s="48">
+        <v>4.82</v>
+      </c>
+      <c r="F55" s="58">
+        <v>1E-4</v>
+      </c>
+      <c r="G55" s="125"/>
+      <c r="H55" s="125"/>
+      <c r="I55" s="55">
         <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="K55" s="56" t="str">
+        <v>2.5465607077581862</v>
+      </c>
+      <c r="J55" s="55">
         <f t="shared" si="21"/>
-        <v/>
-      </c>
-      <c r="L55" s="56" t="str">
+        <v>3.9145356619532561</v>
+      </c>
+      <c r="K55" s="56">
         <f t="shared" si="22"/>
-        <v/>
-      </c>
-      <c r="M55" s="56" t="str">
+        <v>2.8253570400599884E-3</v>
+      </c>
+      <c r="L55" s="56">
         <f t="shared" si="23"/>
-        <v/>
-      </c>
-      <c r="N55" s="56" t="str">
+        <v>1.4178066888089344E-36</v>
+      </c>
+      <c r="M55" s="56">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="O55" s="57" t="str">
+        <v>1</v>
+      </c>
+      <c r="N55" s="56">
         <f t="shared" si="25"/>
-        <v/>
-      </c>
-      <c r="P55" s="57" t="str">
+        <v>3.6377921501801176E-37</v>
+      </c>
+      <c r="O55" s="57">
         <f t="shared" si="26"/>
-        <v/>
-      </c>
-      <c r="Q55" s="57" t="str">
+        <v>2.8407910578774368E-7</v>
+      </c>
+      <c r="P55" s="57">
         <f t="shared" si="27"/>
-        <v/>
-      </c>
-      <c r="R55" s="7"/>
+        <v>2.3333234954083133E-3</v>
+      </c>
+      <c r="Q55" s="57">
+        <f t="shared" si="28"/>
+        <v>1.8768920390981925E-2</v>
+      </c>
+      <c r="R55" s="9">
+        <f t="shared" si="10"/>
+        <v>2.8407910578774368E-3</v>
+      </c>
       <c r="S55" s="7"/>
       <c r="T55" s="7"/>
       <c r="U55" s="7"/>
@@ -16986,42 +17224,42 @@
       <c r="D56" s="48"/>
       <c r="E56" s="48"/>
       <c r="F56" s="58"/>
-      <c r="G56" s="154"/>
-      <c r="H56" s="154"/>
+      <c r="G56" s="125"/>
+      <c r="H56" s="125"/>
       <c r="I56" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J56" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K56" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L56" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M56" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N56" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O56" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P56" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q56" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R56" s="7"/>
@@ -17047,42 +17285,42 @@
       <c r="D57" s="48"/>
       <c r="E57" s="48"/>
       <c r="F57" s="58"/>
-      <c r="G57" s="154"/>
-      <c r="H57" s="154"/>
+      <c r="G57" s="125"/>
+      <c r="H57" s="125"/>
       <c r="I57" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J57" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K57" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L57" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M57" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N57" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O57" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P57" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q57" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R57" s="7"/>
@@ -17108,42 +17346,42 @@
       <c r="D58" s="48"/>
       <c r="E58" s="48"/>
       <c r="F58" s="58"/>
-      <c r="G58" s="154"/>
-      <c r="H58" s="154"/>
+      <c r="G58" s="125"/>
+      <c r="H58" s="125"/>
       <c r="I58" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J58" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K58" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L58" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M58" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N58" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O58" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P58" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q58" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R58" s="7"/>
@@ -17169,42 +17407,42 @@
       <c r="D59" s="48"/>
       <c r="E59" s="48"/>
       <c r="F59" s="58"/>
-      <c r="G59" s="154"/>
-      <c r="H59" s="154"/>
+      <c r="G59" s="125"/>
+      <c r="H59" s="125"/>
       <c r="I59" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J59" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K59" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L59" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M59" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N59" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O59" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P59" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q59" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R59" s="7"/>
@@ -17230,42 +17468,42 @@
       <c r="D60" s="48"/>
       <c r="E60" s="48"/>
       <c r="F60" s="58"/>
-      <c r="G60" s="154"/>
-      <c r="H60" s="154"/>
+      <c r="G60" s="125"/>
+      <c r="H60" s="125"/>
       <c r="I60" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J60" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K60" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L60" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M60" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N60" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O60" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P60" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q60" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R60" s="7"/>
@@ -17291,42 +17529,42 @@
       <c r="D61" s="48"/>
       <c r="E61" s="48"/>
       <c r="F61" s="58"/>
-      <c r="G61" s="154"/>
-      <c r="H61" s="154"/>
+      <c r="G61" s="125"/>
+      <c r="H61" s="125"/>
       <c r="I61" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J61" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K61" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L61" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M61" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N61" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O61" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P61" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q61" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R61" s="7"/>
@@ -17352,42 +17590,42 @@
       <c r="D62" s="48"/>
       <c r="E62" s="48"/>
       <c r="F62" s="58"/>
-      <c r="G62" s="154"/>
-      <c r="H62" s="154"/>
+      <c r="G62" s="125"/>
+      <c r="H62" s="125"/>
       <c r="I62" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J62" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K62" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L62" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M62" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N62" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O62" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P62" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q62" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R62" s="7"/>
@@ -17413,42 +17651,42 @@
       <c r="D63" s="48"/>
       <c r="E63" s="48"/>
       <c r="F63" s="58"/>
-      <c r="G63" s="154"/>
-      <c r="H63" s="154"/>
+      <c r="G63" s="125"/>
+      <c r="H63" s="125"/>
       <c r="I63" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J63" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K63" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L63" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M63" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N63" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O63" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P63" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q63" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R63" s="7"/>
@@ -17474,42 +17712,42 @@
       <c r="D64" s="48"/>
       <c r="E64" s="48"/>
       <c r="F64" s="58"/>
-      <c r="G64" s="154"/>
-      <c r="H64" s="154"/>
+      <c r="G64" s="125"/>
+      <c r="H64" s="125"/>
       <c r="I64" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J64" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K64" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L64" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M64" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N64" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O64" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P64" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q64" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R64" s="7"/>
@@ -17535,42 +17773,42 @@
       <c r="D65" s="48"/>
       <c r="E65" s="48"/>
       <c r="F65" s="58"/>
-      <c r="G65" s="154"/>
-      <c r="H65" s="154"/>
+      <c r="G65" s="125"/>
+      <c r="H65" s="125"/>
       <c r="I65" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J65" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K65" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L65" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M65" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N65" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O65" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P65" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q65" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R65" s="7"/>
@@ -17596,42 +17834,42 @@
       <c r="D66" s="48"/>
       <c r="E66" s="48"/>
       <c r="F66" s="58"/>
-      <c r="G66" s="154"/>
-      <c r="H66" s="154"/>
+      <c r="G66" s="125"/>
+      <c r="H66" s="125"/>
       <c r="I66" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J66" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K66" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L66" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M66" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N66" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O66" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P66" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q66" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R66" s="7"/>
@@ -17657,42 +17895,42 @@
       <c r="D67" s="48"/>
       <c r="E67" s="48"/>
       <c r="F67" s="58"/>
-      <c r="G67" s="154"/>
-      <c r="H67" s="154"/>
+      <c r="G67" s="125"/>
+      <c r="H67" s="125"/>
       <c r="I67" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J67" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K67" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L67" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M67" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N67" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O67" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P67" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q67" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R67" s="7"/>
@@ -17718,42 +17956,42 @@
       <c r="D68" s="48"/>
       <c r="E68" s="48"/>
       <c r="F68" s="58"/>
-      <c r="G68" s="154"/>
-      <c r="H68" s="154"/>
+      <c r="G68" s="125"/>
+      <c r="H68" s="125"/>
       <c r="I68" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J68" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K68" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L68" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M68" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N68" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O68" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P68" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q68" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R68" s="7"/>
@@ -17779,42 +18017,42 @@
       <c r="D69" s="48"/>
       <c r="E69" s="48"/>
       <c r="F69" s="58"/>
-      <c r="G69" s="154"/>
-      <c r="H69" s="154"/>
+      <c r="G69" s="125"/>
+      <c r="H69" s="125"/>
       <c r="I69" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J69" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K69" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L69" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M69" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N69" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O69" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P69" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q69" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R69" s="7"/>
@@ -17840,42 +18078,42 @@
       <c r="D70" s="48"/>
       <c r="E70" s="48"/>
       <c r="F70" s="58"/>
-      <c r="G70" s="154"/>
-      <c r="H70" s="154"/>
+      <c r="G70" s="125"/>
+      <c r="H70" s="125"/>
       <c r="I70" s="55" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
         <v/>
       </c>
       <c r="J70" s="55" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="21"/>
         <v/>
       </c>
       <c r="K70" s="56" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="22"/>
         <v/>
       </c>
       <c r="L70" s="56" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="23"/>
         <v/>
       </c>
       <c r="M70" s="56" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="24"/>
         <v/>
       </c>
       <c r="N70" s="56" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="25"/>
         <v/>
       </c>
       <c r="O70" s="57" t="str">
-        <f t="shared" si="25"/>
+        <f t="shared" si="26"/>
         <v/>
       </c>
       <c r="P70" s="57" t="str">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v/>
       </c>
       <c r="Q70" s="57" t="str">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v/>
       </c>
       <c r="R70" s="7"/>
@@ -17901,42 +18139,42 @@
       <c r="D71" s="48"/>
       <c r="E71" s="48"/>
       <c r="F71" s="58"/>
-      <c r="G71" s="154"/>
-      <c r="H71" s="154"/>
+      <c r="G71" s="125"/>
+      <c r="H71" s="125"/>
       <c r="I71" s="55" t="str">
-        <f t="shared" ref="I71:I122" si="28">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
+        <f t="shared" ref="I71:I122" si="29">IF(D71=0,"",LOG($K$15*10^D71+$K$16*10^E71+$K$14))</f>
         <v/>
       </c>
       <c r="J71" s="55" t="str">
-        <f t="shared" ref="J71:J122" si="29">IF(D71=0,"",LOG($K$21*10^D71+$K$22*10^E71+$K$20))</f>
+        <f t="shared" ref="J71:J122" si="30">IF(D71=0,"",LOG($K$21*10^D71+$K$22*10^E71+$K$20))</f>
         <v/>
       </c>
       <c r="K71" s="56" t="str">
-        <f t="shared" ref="K71:K122" si="30">IF(D71=0,"",1/(1+10^D71*$J$15/$J$14+10^E71*$J$16/$J$14+10^J71*$J$19/$J$14))</f>
+        <f t="shared" ref="K71:K122" si="31">IF(D71=0,"",1/(1+10^D71*$J$15/$J$14+10^E71*$J$16/$J$14+10^J71*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L71" s="56" t="str">
-        <f t="shared" ref="L71:L122" si="31">IF(D71=0,"",1/(1+10^I71/10^J71*$J$13/$J$19))</f>
+        <f t="shared" ref="L71:L122" si="32">IF(D71=0,"",1/(1+10^I71/10^J71*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M71" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N71" s="56" t="str">
-        <f t="shared" ref="N71:N122" si="32">IF(D71=0,"",1/(1/10^E71*$J$20/$J$22+10^D71/10^E71*$J$21/$J$22+10^I71/10^E71*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N71:N122" si="33">IF(D71=0,"",1/(1/10^E71*$J$20/$J$22+10^D71/10^E71*$J$21/$J$22+10^I71/10^E71*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O71" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P71" s="57" t="str">
-        <f t="shared" ref="P71:P122" si="33">IF(D71=0,"",O71*10^J71)</f>
+        <f t="shared" ref="P71:P122" si="34">IF(D71=0,"",O71*10^J71)</f>
         <v/>
       </c>
       <c r="Q71" s="57" t="str">
-        <f t="shared" ref="Q71:Q122" si="34">IF(D71=0,"",F71*N71*$J$7/$J$22)</f>
+        <f t="shared" ref="Q71:Q122" si="35">IF(D71=0,"",F71*N71*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R71" s="7"/>
@@ -17962,42 +18200,42 @@
       <c r="D72" s="48"/>
       <c r="E72" s="48"/>
       <c r="F72" s="58"/>
-      <c r="G72" s="154"/>
-      <c r="H72" s="154"/>
+      <c r="G72" s="125"/>
+      <c r="H72" s="125"/>
       <c r="I72" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J72" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K72" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L72" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M72" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N72" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O72" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P72" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q72" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R72" s="7"/>
@@ -18023,42 +18261,42 @@
       <c r="D73" s="48"/>
       <c r="E73" s="48"/>
       <c r="F73" s="58"/>
-      <c r="G73" s="154"/>
-      <c r="H73" s="154"/>
+      <c r="G73" s="125"/>
+      <c r="H73" s="125"/>
       <c r="I73" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J73" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K73" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L73" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M73" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N73" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O73" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P73" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q73" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R73" s="7"/>
@@ -18084,42 +18322,42 @@
       <c r="D74" s="48"/>
       <c r="E74" s="48"/>
       <c r="F74" s="58"/>
-      <c r="G74" s="154"/>
-      <c r="H74" s="154"/>
+      <c r="G74" s="125"/>
+      <c r="H74" s="125"/>
       <c r="I74" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J74" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K74" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L74" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M74" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N74" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O74" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P74" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q74" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R74" s="7"/>
@@ -18145,42 +18383,42 @@
       <c r="D75" s="48"/>
       <c r="E75" s="48"/>
       <c r="F75" s="58"/>
-      <c r="G75" s="154"/>
-      <c r="H75" s="154"/>
+      <c r="G75" s="125"/>
+      <c r="H75" s="125"/>
       <c r="I75" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J75" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K75" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L75" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M75" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N75" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O75" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P75" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q75" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R75" s="7"/>
@@ -18206,42 +18444,42 @@
       <c r="D76" s="48"/>
       <c r="E76" s="48"/>
       <c r="F76" s="58"/>
-      <c r="G76" s="154"/>
-      <c r="H76" s="154"/>
+      <c r="G76" s="125"/>
+      <c r="H76" s="125"/>
       <c r="I76" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J76" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K76" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L76" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M76" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N76" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O76" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P76" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q76" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R76" s="7"/>
@@ -18267,42 +18505,42 @@
       <c r="D77" s="48"/>
       <c r="E77" s="48"/>
       <c r="F77" s="58"/>
-      <c r="G77" s="154"/>
-      <c r="H77" s="154"/>
+      <c r="G77" s="125"/>
+      <c r="H77" s="125"/>
       <c r="I77" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J77" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K77" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L77" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M77" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N77" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O77" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P77" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q77" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R77" s="7"/>
@@ -18331,39 +18569,39 @@
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
       <c r="I78" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J78" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K78" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L78" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M78" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N78" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O78" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P78" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q78" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R78" s="7"/>
@@ -18392,39 +18630,39 @@
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
       <c r="I79" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J79" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K79" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L79" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M79" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N79" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O79" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P79" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q79" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R79" s="7"/>
@@ -18453,39 +18691,39 @@
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
       <c r="I80" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J80" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K80" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L80" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M80" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N80" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O80" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P80" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q80" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R80" s="7"/>
@@ -18514,39 +18752,39 @@
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
       <c r="I81" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J81" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K81" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L81" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M81" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N81" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O81" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P81" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q81" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R81" s="7"/>
@@ -18575,39 +18813,39 @@
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
       <c r="I82" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J82" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K82" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L82" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M82" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N82" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O82" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P82" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q82" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R82" s="7"/>
@@ -18636,39 +18874,39 @@
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
       <c r="I83" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J83" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K83" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L83" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M83" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N83" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O83" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P83" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q83" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R83" s="7"/>
@@ -18697,39 +18935,39 @@
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
       <c r="I84" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J84" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K84" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L84" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M84" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N84" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O84" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P84" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q84" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R84" s="7"/>
@@ -18758,39 +18996,39 @@
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
       <c r="I85" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J85" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K85" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L85" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M85" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N85" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O85" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P85" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q85" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R85" s="7"/>
@@ -18819,39 +19057,39 @@
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
       <c r="I86" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J86" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K86" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L86" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M86" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N86" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O86" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P86" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q86" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R86" s="7"/>
@@ -18880,39 +19118,39 @@
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
       <c r="I87" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J87" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K87" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L87" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M87" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N87" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O87" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P87" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q87" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R87" s="7"/>
@@ -18941,39 +19179,39 @@
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
       <c r="I88" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J88" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K88" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L88" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M88" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N88" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O88" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P88" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q88" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R88" s="7"/>
@@ -19002,39 +19240,39 @@
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
       <c r="I89" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J89" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K89" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L89" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M89" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N89" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O89" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P89" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q89" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R89" s="7"/>
@@ -19063,39 +19301,39 @@
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
       <c r="I90" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J90" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K90" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L90" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M90" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N90" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O90" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P90" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q90" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R90" s="7"/>
@@ -19124,39 +19362,39 @@
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
       <c r="I91" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J91" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K91" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L91" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M91" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N91" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O91" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P91" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q91" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R91" s="7"/>
@@ -19185,39 +19423,39 @@
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
       <c r="I92" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J92" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K92" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L92" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M92" s="56" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v/>
       </c>
       <c r="N92" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O92" s="57" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v/>
       </c>
       <c r="P92" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q92" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R92" s="7"/>
@@ -19246,39 +19484,39 @@
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
       <c r="I93" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J93" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K93" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L93" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M93" s="56" t="str">
-        <f t="shared" ref="M93:M127" si="35">IF(D93=0,"",1-L93)</f>
+        <f t="shared" ref="M93:M127" si="36">IF(D93=0,"",1-L93)</f>
         <v/>
       </c>
       <c r="N93" s="56" t="str">
-        <f t="shared" si="32"/>
+        <f t="shared" si="33"/>
         <v/>
       </c>
       <c r="O93" s="57" t="str">
-        <f t="shared" ref="O93:O127" si="36">IF(D93=0,"",F93*K93*$J$7/$J$14)</f>
+        <f t="shared" ref="O93:O127" si="37">IF(D93=0,"",F93*K93*$J$7/$J$14)</f>
         <v/>
       </c>
       <c r="P93" s="57" t="str">
-        <f t="shared" si="33"/>
+        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="Q93" s="57" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="35"/>
         <v/>
       </c>
       <c r="R93" s="7"/>
@@ -19307,39 +19545,39 @@
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
       <c r="I94" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J94" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K94" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L94" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M94" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N94" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O94" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P94" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q94" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N94" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O94" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P94" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q94" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R94" s="7"/>
@@ -19368,39 +19606,39 @@
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
       <c r="I95" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J95" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K95" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L95" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M95" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N95" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O95" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P95" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q95" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N95" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O95" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P95" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q95" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R95" s="7"/>
@@ -19429,39 +19667,39 @@
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
       <c r="I96" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J96" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K96" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L96" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M96" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N96" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O96" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P96" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q96" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N96" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O96" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P96" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q96" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R96" s="7"/>
@@ -19490,39 +19728,39 @@
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
       <c r="I97" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J97" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K97" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L97" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M97" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N97" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O97" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P97" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q97" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N97" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O97" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P97" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q97" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R97" s="7"/>
@@ -19551,39 +19789,39 @@
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
       <c r="I98" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J98" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K98" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L98" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M98" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N98" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O98" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P98" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q98" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N98" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O98" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P98" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q98" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R98" s="7"/>
@@ -19612,39 +19850,39 @@
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
       <c r="I99" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J99" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K99" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L99" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M99" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N99" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O99" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P99" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q99" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N99" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O99" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P99" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q99" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R99" s="7"/>
@@ -19673,39 +19911,39 @@
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
       <c r="I100" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J100" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K100" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L100" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M100" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N100" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O100" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P100" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q100" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N100" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O100" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P100" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q100" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R100" s="7"/>
@@ -19734,39 +19972,39 @@
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
       <c r="I101" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J101" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K101" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L101" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M101" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N101" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O101" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P101" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q101" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N101" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O101" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P101" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q101" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R101" s="7"/>
@@ -19795,39 +20033,39 @@
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
       <c r="I102" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J102" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K102" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L102" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M102" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N102" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O102" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P102" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q102" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N102" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O102" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P102" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q102" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R102" s="7"/>
@@ -19856,39 +20094,39 @@
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
       <c r="I103" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J103" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K103" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L103" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M103" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N103" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O103" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P103" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q103" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N103" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O103" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P103" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q103" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R103" s="7"/>
@@ -19917,39 +20155,39 @@
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
       <c r="I104" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J104" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K104" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L104" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M104" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N104" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O104" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P104" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q104" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N104" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O104" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P104" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q104" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R104" s="7"/>
@@ -19978,39 +20216,39 @@
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
       <c r="I105" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J105" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K105" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L105" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M105" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N105" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O105" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P105" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q105" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N105" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O105" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P105" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q105" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R105" s="7"/>
@@ -20039,39 +20277,39 @@
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
       <c r="I106" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J106" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K106" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L106" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M106" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N106" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O106" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P106" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q106" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N106" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O106" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P106" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q106" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R106" s="7"/>
@@ -20100,39 +20338,39 @@
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
       <c r="I107" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J107" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K107" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L107" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M107" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N107" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O107" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P107" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q107" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N107" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O107" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P107" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q107" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R107" s="7"/>
@@ -20161,39 +20399,39 @@
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
       <c r="I108" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J108" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K108" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L108" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M108" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N108" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O108" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P108" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q108" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N108" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O108" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P108" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q108" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R108" s="7"/>
@@ -20222,39 +20460,39 @@
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
       <c r="I109" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J109" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K109" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L109" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M109" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N109" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O109" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P109" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q109" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N109" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O109" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P109" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q109" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R109" s="7"/>
@@ -20283,39 +20521,39 @@
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
       <c r="I110" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J110" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K110" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L110" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M110" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N110" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O110" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P110" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q110" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N110" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O110" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P110" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q110" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R110" s="7"/>
@@ -20344,39 +20582,39 @@
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
       <c r="I111" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J111" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K111" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L111" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M111" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N111" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O111" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P111" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q111" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N111" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O111" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P111" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q111" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R111" s="7"/>
@@ -20405,39 +20643,39 @@
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
       <c r="I112" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J112" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K112" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L112" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M112" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N112" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O112" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P112" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q112" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N112" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O112" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P112" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q112" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R112" s="7"/>
@@ -20466,39 +20704,39 @@
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
       <c r="I113" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J113" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K113" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L113" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M113" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N113" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O113" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P113" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q113" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N113" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O113" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P113" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q113" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R113" s="7"/>
@@ -20527,39 +20765,39 @@
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
       <c r="I114" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J114" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K114" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L114" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M114" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N114" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O114" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P114" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q114" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N114" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O114" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P114" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q114" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R114" s="7"/>
@@ -20588,39 +20826,39 @@
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
       <c r="I115" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J115" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K115" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L115" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M115" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N115" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O115" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P115" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q115" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N115" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O115" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P115" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q115" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R115" s="7"/>
@@ -20649,39 +20887,39 @@
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
       <c r="I116" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J116" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K116" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L116" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M116" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N116" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O116" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P116" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q116" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N116" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O116" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P116" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q116" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R116" s="7"/>
@@ -20710,39 +20948,39 @@
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
       <c r="I117" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J117" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K117" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L117" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M117" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N117" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O117" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P117" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q117" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N117" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O117" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P117" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q117" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R117" s="7"/>
@@ -20771,39 +21009,39 @@
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
       <c r="I118" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J118" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K118" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L118" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M118" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N118" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O118" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P118" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q118" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N118" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O118" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P118" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q118" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R118" s="7"/>
@@ -20832,39 +21070,39 @@
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
       <c r="I119" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J119" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K119" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L119" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M119" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N119" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O119" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P119" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q119" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N119" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O119" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P119" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q119" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R119" s="7"/>
@@ -20893,39 +21131,39 @@
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
       <c r="I120" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J120" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K120" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L120" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M120" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N120" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O120" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P120" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q120" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N120" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O120" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P120" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q120" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R120" s="7"/>
@@ -20954,39 +21192,39 @@
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
       <c r="I121" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J121" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K121" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L121" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M121" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N121" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O121" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P121" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q121" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N121" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O121" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P121" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q121" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R121" s="7"/>
@@ -21015,39 +21253,39 @@
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
       <c r="I122" s="55" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v/>
       </c>
       <c r="J122" s="55" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" si="30"/>
         <v/>
       </c>
       <c r="K122" s="56" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" si="31"/>
         <v/>
       </c>
       <c r="L122" s="56" t="str">
-        <f t="shared" si="31"/>
+        <f t="shared" si="32"/>
         <v/>
       </c>
       <c r="M122" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N122" s="56" t="str">
+        <f t="shared" si="33"/>
+        <v/>
+      </c>
+      <c r="O122" s="57" t="str">
+        <f t="shared" si="37"/>
+        <v/>
+      </c>
+      <c r="P122" s="57" t="str">
+        <f t="shared" si="34"/>
+        <v/>
+      </c>
+      <c r="Q122" s="57" t="str">
         <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N122" s="56" t="str">
-        <f t="shared" si="32"/>
-        <v/>
-      </c>
-      <c r="O122" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
-      <c r="P122" s="57" t="str">
-        <f t="shared" si="33"/>
-        <v/>
-      </c>
-      <c r="Q122" s="57" t="str">
-        <f t="shared" si="34"/>
         <v/>
       </c>
       <c r="R122" s="7"/>
@@ -21076,39 +21314,39 @@
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
       <c r="I123" s="55" t="str">
-        <f t="shared" ref="I123:I127" si="37">IF(D123=0,"",LOG($K$15*10^D123+$K$16*10^E123+$K$14))</f>
+        <f t="shared" ref="I123:I127" si="38">IF(D123=0,"",LOG($K$15*10^D123+$K$16*10^E123+$K$14))</f>
         <v/>
       </c>
       <c r="J123" s="55" t="str">
-        <f t="shared" ref="J123:J127" si="38">IF(D123=0,"",LOG($K$21*10^D123+$K$22*10^E123+$K$20))</f>
+        <f t="shared" ref="J123:J127" si="39">IF(D123=0,"",LOG($K$21*10^D123+$K$22*10^E123+$K$20))</f>
         <v/>
       </c>
       <c r="K123" s="56" t="str">
-        <f t="shared" ref="K123:K127" si="39">IF(D123=0,"",1/(1+10^D123*$J$15/$J$14+10^E123*$J$16/$J$14+10^J123*$J$19/$J$14))</f>
+        <f t="shared" ref="K123:K127" si="40">IF(D123=0,"",1/(1+10^D123*$J$15/$J$14+10^E123*$J$16/$J$14+10^J123*$J$19/$J$14))</f>
         <v/>
       </c>
       <c r="L123" s="56" t="str">
-        <f t="shared" ref="L123:L127" si="40">IF(D123=0,"",1/(1+10^I123/10^J123*$J$13/$J$19))</f>
+        <f t="shared" ref="L123:L127" si="41">IF(D123=0,"",1/(1+10^I123/10^J123*$J$13/$J$19))</f>
         <v/>
       </c>
       <c r="M123" s="56" t="str">
-        <f t="shared" si="35"/>
+        <f t="shared" si="36"/>
         <v/>
       </c>
       <c r="N123" s="56" t="str">
-        <f t="shared" ref="N123:N127" si="41">IF(D123=0,"",1/(1/10^E123*$J$20/$J$22+10^D123/10^E123*$J$21/$J$22+10^I123/10^E123*$J$13/$J$22+1))</f>
+        <f t="shared" ref="N123:N127" si="42">IF(D123=0,"",1/(1/10^E123*$J$20/$J$22+10^D123/10^E123*$J$21/$J$22+10^I123/10^E123*$J$13/$J$22+1))</f>
         <v/>
       </c>
       <c r="O123" s="57" t="str">
-        <f t="shared" si="36"/>
+        <f t="shared" si="37"/>
         <v/>
       </c>
       <c r="P123" s="57" t="str">
-        <f t="shared" ref="P123:P127" si="42">IF(D123=0,"",O123*10^J123)</f>
+        <f t="shared" ref="P123:P127" si="43">IF(D123=0,"",O123*10^J123)</f>
         <v/>
       </c>
       <c r="Q123" s="57" t="str">
-        <f t="shared" ref="Q123:Q127" si="43">IF(D123=0,"",F123*N123*$J$7/$J$22)</f>
+        <f t="shared" ref="Q123:Q127" si="44">IF(D123=0,"",F123*N123*$J$7/$J$22)</f>
         <v/>
       </c>
       <c r="R123" s="7"/>
@@ -21137,39 +21375,39 @@
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
       <c r="I124" s="55" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J124" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K124" s="56" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="L124" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="M124" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N124" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="O124" s="57" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J124" s="55" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K124" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L124" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M124" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N124" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O124" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P124" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q124" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="R124" s="7"/>
@@ -21198,39 +21436,39 @@
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
       <c r="I125" s="55" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J125" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K125" s="56" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="L125" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="M125" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N125" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="O125" s="57" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J125" s="55" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K125" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L125" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M125" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N125" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O125" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P125" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q125" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="R125" s="7"/>
@@ -21259,39 +21497,39 @@
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
       <c r="I126" s="55" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J126" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K126" s="56" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="L126" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="M126" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N126" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="O126" s="57" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J126" s="55" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K126" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L126" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M126" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N126" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O126" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P126" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q126" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="R126" s="7"/>
@@ -21320,39 +21558,39 @@
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
       <c r="I127" s="55" t="str">
+        <f t="shared" si="38"/>
+        <v/>
+      </c>
+      <c r="J127" s="55" t="str">
+        <f t="shared" si="39"/>
+        <v/>
+      </c>
+      <c r="K127" s="56" t="str">
+        <f t="shared" si="40"/>
+        <v/>
+      </c>
+      <c r="L127" s="56" t="str">
+        <f t="shared" si="41"/>
+        <v/>
+      </c>
+      <c r="M127" s="56" t="str">
+        <f t="shared" si="36"/>
+        <v/>
+      </c>
+      <c r="N127" s="56" t="str">
+        <f t="shared" si="42"/>
+        <v/>
+      </c>
+      <c r="O127" s="57" t="str">
         <f t="shared" si="37"/>
         <v/>
       </c>
-      <c r="J127" s="55" t="str">
-        <f t="shared" si="38"/>
-        <v/>
-      </c>
-      <c r="K127" s="56" t="str">
-        <f t="shared" si="39"/>
-        <v/>
-      </c>
-      <c r="L127" s="56" t="str">
-        <f t="shared" si="40"/>
-        <v/>
-      </c>
-      <c r="M127" s="56" t="str">
-        <f t="shared" si="35"/>
-        <v/>
-      </c>
-      <c r="N127" s="56" t="str">
-        <f t="shared" si="41"/>
-        <v/>
-      </c>
-      <c r="O127" s="57" t="str">
-        <f t="shared" si="36"/>
-        <v/>
-      </c>
       <c r="P127" s="57" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="43"/>
         <v/>
       </c>
       <c r="Q127" s="57" t="str">
-        <f t="shared" si="43"/>
+        <f t="shared" si="44"/>
         <v/>
       </c>
       <c r="R127" s="7"/>
@@ -24981,21 +25219,27 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="L8:Q8"/>
-    <mergeCell ref="L9:Q9"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="I24:Q25"/>
-    <mergeCell ref="I23:Q23"/>
-    <mergeCell ref="Q26:Q27"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="J26:J27"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="K26:K27"/>
-    <mergeCell ref="L10:Q10"/>
-    <mergeCell ref="I11:Q11"/>
-    <mergeCell ref="L12:Q12"/>
-    <mergeCell ref="L13:Q13"/>
-    <mergeCell ref="M26:M27"/>
+    <mergeCell ref="I2:Q4"/>
+    <mergeCell ref="I5:Q5"/>
+    <mergeCell ref="B23:F23"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B8:F10"/>
+    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="L19:Q19"/>
+    <mergeCell ref="L20:Q20"/>
+    <mergeCell ref="L21:Q21"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="L14:Q14"/>
     <mergeCell ref="L15:Q15"/>
@@ -25012,27 +25256,21 @@
     <mergeCell ref="I17:Q17"/>
     <mergeCell ref="B26:B27"/>
     <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="L19:Q19"/>
-    <mergeCell ref="L20:Q20"/>
-    <mergeCell ref="L21:Q21"/>
-    <mergeCell ref="I2:Q4"/>
-    <mergeCell ref="I5:Q5"/>
-    <mergeCell ref="B23:F23"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="B19:F19"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B8:F10"/>
-    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="L8:Q8"/>
+    <mergeCell ref="L9:Q9"/>
+    <mergeCell ref="P26:P27"/>
+    <mergeCell ref="I24:Q25"/>
+    <mergeCell ref="I23:Q23"/>
+    <mergeCell ref="Q26:Q27"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="J26:J27"/>
+    <mergeCell ref="O26:O27"/>
+    <mergeCell ref="K26:K27"/>
+    <mergeCell ref="L10:Q10"/>
+    <mergeCell ref="I11:Q11"/>
+    <mergeCell ref="L12:Q12"/>
+    <mergeCell ref="L13:Q13"/>
+    <mergeCell ref="M26:M27"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
